--- a/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
@@ -575,46 +575,46 @@
         <v>144</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.228783902012879</v>
+        <v>7.204838941031795</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.007889334830551</v>
+        <v>6.984617295212779</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.614645142103996</v>
+        <v>6.592449782140847</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.441604328739601</v>
+        <v>7.417007113901228</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.38035090099656</v>
+        <v>10.34582990327002</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.290099329498481</v>
+        <v>9.259374544161538</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.9894433829057</v>
+        <v>11.95018941050531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.91574457296043</v>
+        <v>12.87356343957169</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.46617173578678</v>
+        <v>11.42874984498827</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.31287101415475</v>
+        <v>11.27616930607047</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>14.59142536095365</v>
+        <v>14.54398274011533</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.62956568577924</v>
+        <v>14.58199574163166</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.21160456922966</v>
+        <v>14.16551416816576</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.16245154432657</v>
+        <v>15.11322536035286</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>144</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.367672790900976</v>
+        <v>2.358469462725296</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.924145376000318</v>
+        <v>4.9062114678445</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.140861217165984</v>
+        <v>3.128816924852309</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.202861577425729</v>
+        <v>-0.2032917174001696</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7416082711770855</v>
+        <v>-0.7408730704502418</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.64208849944395</v>
+        <v>1.635080761138688</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.426514217451832</v>
+        <v>6.403236399830327</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.83030158250332</v>
+        <v>10.79203838377341</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.07610761713723</v>
+        <v>10.04059547469985</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.226537091832327</v>
+        <v>9.194169567843687</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.024043816864364</v>
+        <v>8.991974981120208</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.54325855065963</v>
+        <v>12.49920309953183</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.9114564970432</v>
+        <v>14.85950798899641</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.37891076861737</v>
+        <v>12.3354475825754</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6980510414921497</v>
+        <v>0.694035895538299</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.924027596645693</v>
+        <v>1.915308035229089</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.787242886883163</v>
+        <v>5.764911594837422</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.209362070736454</v>
+        <v>5.18976893529782</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.672063243676895</v>
+        <v>4.653720631057624</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.391661886197518</v>
+        <v>6.367323626020436</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.598572909437543</v>
+        <v>5.576417728841797</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.843091963769766</v>
+        <v>5.819491275481028</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.46972113669438</v>
+        <v>11.42653146942086</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.198654403961456</v>
+        <v>9.163877345063852</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.707482522034596</v>
+        <v>9.67051310952138</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.16792033952841</v>
+        <v>11.12531230361927</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.74970265778712</v>
+        <v>10.70843861823301</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.29156752387583</v>
+        <v>10.25211424924223</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>144</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.187882764654582</v>
+        <v>-3.177927106170777</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.022070382277199</v>
+        <v>-2.016977210608296</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.027802616199686</v>
+        <v>-1.026865324966927</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.272503318545816</v>
+        <v>3.258454925659059</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.741410327636693</v>
+        <v>-0.7413184434165956</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2519334487374181</v>
+        <v>0.2482177311571192</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.223650900025397</v>
+        <v>-1.222496889038247</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.691492963632498</v>
+        <v>-1.689280576682116</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.144551465919086</v>
+        <v>-3.137464820611889</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.997905102795428</v>
+        <v>-3.986942543186146</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.900116472062912</v>
+        <v>-4.886332487757386</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.259303017549556</v>
+        <v>-6.241240251702486</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.895061878129681</v>
+        <v>-3.885782146406015</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.645407525843815</v>
+        <v>-3.636774639646823</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>141</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-9.231026972692241</v>
+        <v>-9.197081264879664</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.007910016997933</v>
+        <v>-7.979454785447935</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.985818399787846</v>
+        <v>-6.961974732725977</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.40657673076283</v>
+        <v>-10.36939487057926</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.398196542765263</v>
+        <v>-7.372592012568091</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.971364718189683</v>
+        <v>-4.955379906250585</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.188735701431455</v>
+        <v>-7.164630026562804</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.237022787728705</v>
+        <v>-6.217208745018276</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.166831649221159</v>
+        <v>-4.155232968460098</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.731865359289401</v>
+        <v>-5.713338457557533</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.227029686783048</v>
+        <v>-5.210835355492854</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.481774471910384</v>
+        <v>-4.469004951812366</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.192341043387096</v>
+        <v>-4.181142846385256</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.790570798603454</v>
+        <v>-6.769162346502618</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>144</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.367672790901139</v>
+        <v>2.35818711361042</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6329006484358786</v>
+        <v>-0.6314584611457192</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.751507797910293</v>
+        <v>1.74248295298171</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4922140241426334</v>
+        <v>0.4890488699646554</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.820647308292159</v>
+        <v>4.799607431300025</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.424943998908127</v>
+        <v>4.404734184217631</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.645899757598961</v>
+        <v>3.628768084474309</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.692114618312978</v>
+        <v>-1.688747729812953</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.145439242213442</v>
+        <v>-3.136909960428333</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.999468186388498</v>
+        <v>-3.986247839366783</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.20547466190753</v>
+        <v>-4.191947253025901</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-7.655405638296536</v>
+        <v>-7.628817552981296</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.381741600765224</v>
+        <v>-7.35679957692701</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.133656011605197</v>
+        <v>-7.108996861868732</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>141</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.266487965600049</v>
+        <v>-4.249094404857921</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.042078409982587</v>
+        <v>-3.030426977429357</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-10.53463982218806</v>
+        <v>-10.49310229959526</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.858194600848698</v>
+        <v>-6.83090504357768</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-11.65978025717666</v>
+        <v>-11.61381588918548</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.65474927840058</v>
+        <v>-10.61373765955883</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-10.74285483261401</v>
+        <v>-10.70137283687377</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-10.50349747809106</v>
+        <v>-10.46296600130308</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.145407035801782</v>
+        <v>-9.110999238371612</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.156612895935332</v>
+        <v>-7.128974698165898</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.786772028362194</v>
+        <v>-8.752841731033328</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-10.17821784613852</v>
+        <v>-10.13863936088217</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-9.890584389435546</v>
+        <v>-9.852861338233751</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-6.794664794777248</v>
+        <v>-6.769162346502938</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>144</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7.228783902012246</v>
+        <v>7.197432061450023</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>12.56593815275304</v>
+        <v>12.51025370236511</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.09036485228054</v>
+        <v>10.04543582061248</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.61438853389847</v>
+        <v>11.56328198559302</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.55627223531999</v>
+        <v>14.49167356770921</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>16.25082341575626</v>
+        <v>16.17777156170506</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16.86734190904105</v>
+        <v>16.79171520408779</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>17.79705626692864</v>
+        <v>17.71735976537664</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20.5278002925723</v>
+        <v>20.43537088588602</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>26.64690822995541</v>
+        <v>26.5289428891718</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>25.05717118197173</v>
+        <v>24.94592566047662</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>27.19129032308398</v>
+        <v>27.07077308030341</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>28.17388616290608</v>
+        <v>28.04828699832265</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>29.82923522737241</v>
+        <v>29.69655869368667</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>144</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.187882764654262</v>
+        <v>-3.174416400754012</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7566323556901651</v>
+        <v>0.7497010448946</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.892486803133089</v>
+        <v>-5.868324519056507</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.849557761276131</v>
+        <v>-7.816156289750353</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.218328462202692</v>
+        <v>-4.202974862864849</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.138249918401854</v>
+        <v>-1.138599992531738</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.864636105079974</v>
+        <v>0.8550571605612021</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.966516779397615</v>
+        <v>5.933219008657623</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.908803612219181</v>
+        <v>5.874327144440038</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.451907805705382</v>
+        <v>6.414992460442825</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.339963054457698</v>
+        <v>8.294421432064198</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.378320983465073</v>
+        <v>8.332222051143205</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.96082469145427</v>
+        <v>7.915579157980467</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.215369003064311</v>
+        <v>8.168780915908741</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7203886748200645</v>
+        <v>-0.7174633745464263</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.343352030445331</v>
+        <v>3.323131141691924</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.239666319806382</v>
+        <v>2.226937323690137</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2408333240170748</v>
+        <v>0.2385290602969619</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.123068525003049</v>
+        <v>1.114136053037605</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.261677352889926</v>
+        <v>-4.246908059524131</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.92588889817813</v>
+        <v>-2.918093140996902</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.105173617137858</v>
+        <v>-4.093140252941353</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.877650908419284</v>
+        <v>-4.863453200964408</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-8.57813575924412</v>
+        <v>-8.546044126923547</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.497716179371636</v>
+        <v>-9.461544301332864</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.31419515790214</v>
+        <v>-12.26478661947871</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-12.73915541513366</v>
+        <v>-12.68876647143472</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.20453812190197</v>
+        <v>-13.15214106990687</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>144</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.965660542432197</v>
+        <v>-5.935507532156016</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-10.35868675028451</v>
+        <v>-10.31091412785239</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.45294946510771</v>
+        <v>-11.39689098930636</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.3271703607303</v>
+        <v>-11.27041058786573</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-11.86993750075863</v>
+        <v>-11.81324341500272</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-11.57579663298994</v>
+        <v>-11.52185858252339</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.57619453662678</v>
+        <v>-9.533418201892609</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.43998578850639</v>
+        <v>-11.38898513948789</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.20079807752911</v>
+        <v>-12.14744957724483</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.877203613991782</v>
+        <v>-8.839970365370519</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-8.388312003820054</v>
+        <v>-8.353762717119452</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.356687299525071</v>
+        <v>-8.322018867101022</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-8.082863147191553</v>
+        <v>-8.050687596206309</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-7.136164843727201</v>
+        <v>-7.108996861869045</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>97</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.070757907839074</v>
+        <v>-5.04239606194885</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.684862698402327</v>
+        <v>-6.651957389615859</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-9.146640843839521</v>
+        <v>-9.097338692651903</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.955961455466479</v>
+        <v>-6.916899225878424</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-14.72571733501761</v>
+        <v>-14.6481912506918</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.201751931573604</v>
+        <v>-7.165805477068986</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-12.45608130457292</v>
+        <v>-12.39372021813519</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-11.89503791399169</v>
+        <v>-11.83656932648106</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-12.99416099988627</v>
+        <v>-12.93130851824025</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-13.85229849502223</v>
+        <v>-13.78485628562485</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-18.20353521259313</v>
+        <v>-18.11323355517455</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-18.17622860075507</v>
+        <v>-18.08577299477471</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-22.74847677877628</v>
+        <v>-22.63492006085198</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-21.46928724578024</v>
+        <v>-21.36300602567203</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>96</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.576771653542835</v>
+        <v>-4.548814583506413</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.148762474729246</v>
+        <v>-5.121672101174759</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.376455134879812</v>
+        <v>-1.366220916671388</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.838933529263727</v>
+        <v>0.837946815858345</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7433208941731593</v>
+        <v>-0.737019668710083</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4444787289241674</v>
+        <v>-0.4430783401395573</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5150698750706297</v>
+        <v>0.5105696140906417</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.04742669591819748</v>
+        <v>0.04442320719552129</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.077760943180074</v>
+        <v>2.062131590367457</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.911634354745061</v>
+        <v>-1.904914727504647</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.118240876490098</v>
+        <v>-2.109784055317746</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.177784176970903</v>
+        <v>-4.157577010595638</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.648449264834312</v>
+        <v>-5.620453567884077</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.303758660536026</v>
+        <v>-3.289552417424837</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.912793158919833</v>
+        <v>-5.566195107740612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.701489865130782</v>
+        <v>-8.595469926409038</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.418546203597579</v>
+        <v>-4.999611139501219</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.844865063880256</v>
+        <v>-4.371745914583009</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.348485820389456</v>
+        <v>-7.143346466515219</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-9.673963445251211</v>
+        <v>-10.78565217651003</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-12.54857735552642</v>
+        <v>-13.97971048821718</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.14214675061143</v>
+        <v>-11.26955169924999</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.58673798362133</v>
+        <v>-11.72668504570127</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.889779386727767</v>
+        <v>-7.620395032031695</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.815003856440164</v>
+        <v>-6.433703394798947</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.127773861220433</v>
+        <v>-6.799980505528268</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.251425902546082</v>
+        <v>-5.819824149886543</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-7.825236775933639</v>
+        <v>-8.666804669676651</v>
       </c>
     </row>
     <row r="20">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 28.82</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.07074535697646667</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 76.41</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3950~3963</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3950</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.3359818478405643</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 124</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3806~3819</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3806</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.4379264060963379</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 171.6</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3665~3678</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3665</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.4814752968277105</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 219.2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3521~3534</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3521</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3711972336225386</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 266.8</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3380~3393</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3380</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.003016864271280895</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 314.4</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3236~3249</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3236</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1080889819520507</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 362</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3095~3108</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3095</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.0805642537926019</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 409.6</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2951~2964</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2951</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2667176724366911</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 457.2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2807~2820</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2807</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1175517953872856</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 504.7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2666~2679</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2666</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.08582353857504188</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 552.3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2522~2535</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2522</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.2481790367919956</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 599.9</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2425~2438</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2425</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.4598020407416286</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 647.5</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2329~2342</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2329</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.6662542502426234</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 695.1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2218~2218</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2218</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.9781577122517007</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 742.7</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2077~2077</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2077</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.286051328321555</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 790.3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1933~1933</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1933</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.360674457855211</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 837.9</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1792~1792</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1792</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.915043822647164</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 885.5</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1648~1648</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1648</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.360930611828856</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 933.1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1504~1504</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1504</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.227306360641087</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 980.7</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1363~1363</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1363</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.605607901360095</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1028</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1219~1219</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1219</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.551680629749008</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1076</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1078~1078</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1078</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.072424388509873</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1123</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>934~934</t>
-        </is>
+      <c r="B29" t="n">
+        <v>934</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.324548831824288</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1171</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>790~790</t>
-        </is>
+      <c r="B30" t="n">
+        <v>790</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.202764211435593</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1219</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>649~649</t>
-        </is>
+      <c r="B31" t="n">
+        <v>649</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.514265840036551</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1266</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>505~505</t>
-        </is>
+      <c r="B32" t="n">
+        <v>505</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.5758686104830986</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1314</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>364~364</t>
-        </is>
+      <c r="B33" t="n">
+        <v>364</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-2.218713045484705</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1361</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>220~220</t>
-        </is>
+      <c r="B34" t="n">
+        <v>220</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-3.857074683846335</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1409</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.5186098725611146</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 28.82</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3.458942632170981</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 76.41</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>228~228</t>
-        </is>
+      <c r="B7" t="n">
+        <v>228</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5.83989501312336</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 124</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>372~372</t>
-        </is>
+      <c r="B8" t="n">
+        <v>372</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.495808991617984</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 171.6</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>513~513</t>
-        </is>
+      <c r="B9" t="n">
+        <v>513</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.45198078310387</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 219.2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>657~657</t>
-        </is>
+      <c r="B10" t="n">
+        <v>657</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.996668224691085</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 266.8</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>798~798</t>
-        </is>
+      <c r="B11" t="n">
+        <v>798</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.01282734395042695</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 314.4</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>942~942</t>
-        </is>
+      <c r="B12" t="n">
+        <v>942</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.3728037180065868</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 362</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1083~1083</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1083</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2312037865072938</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 409.6</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1227~1227</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1227</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.6442959911184687</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 457.2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1371~1371</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1371</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.241791439089809</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 504.7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1512~1512</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1512</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1520643252926774</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 552.3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1656~1656</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1656</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3799117501616678</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 599.9</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1753~1753</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1753</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6394736881506518</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 647.5</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1849~1849</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1849</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.8438980281602184</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 695.1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1960~1973</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1960</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.099621797148643</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 742.7</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2101~2114</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2101</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.263542388327288</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 790.3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2245~2258</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2245</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.164828931370288</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 837.9</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2386~2399</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2386</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.430495427337945</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 885.5</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2530~2543</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2530</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.530009299368452</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 933.1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2674~2687</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2674</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.246694740009005</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 980.7</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2815~2828</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2815</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.255814557833737</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1028</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2959~2972</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2959</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.046601173507412</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1076</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3100~3113</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3100</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.063949081533458</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1123</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3244~3257</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3244</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.6666038099244389</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1171</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3388~3401</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3388</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.7439528747527504</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1219</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3529~3542</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3529</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4606884613731594</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1266</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3673~3686</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3673</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.07889681179976549</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1314</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3814~3827</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3814</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.2110299316844575</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1361</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3958~3971</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3958</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.213688348135527</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1409</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4093~4106</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.03362341519293466</v>

--- a/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days To Halving is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days To Halving is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 52.61</t>
+          <t>X ≈ 52.64</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>144</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.204838941031795</v>
+        <v>7.193550291594576</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.984617295212779</v>
+        <v>6.997492698631739</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.592449782140847</v>
+        <v>6.605424904749498</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.417007113901228</v>
+        <v>7.429957630165539</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.34582990327002</v>
+        <v>10.35891641494135</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.259374544161538</v>
+        <v>9.272395358321504</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.95018941050531</v>
+        <v>11.96323741334275</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.87356343957169</v>
+        <v>12.8867289519949</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.42874984498827</v>
+        <v>11.44193518056456</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.27616930607047</v>
+        <v>11.28956342285053</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>14.54398274011533</v>
+        <v>14.55743235922945</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.58199574163166</v>
+        <v>14.59544292024463</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.16551416816576</v>
+        <v>14.17906760116425</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.11322536035286</v>
+        <v>15.10279572465503</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>144</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.358469462725296</v>
+        <v>2.347180273212125</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.9062114678445</v>
+        <v>4.919082986351469</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.128816924852309</v>
+        <v>3.1417873832658</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2032917174001696</v>
+        <v>-0.1903482313644318</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7408730704502418</v>
+        <v>-0.7277947884534939</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.635080761138688</v>
+        <v>1.648096082569616</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.403236399830327</v>
+        <v>6.416280768959794</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.79203838377341</v>
+        <v>10.80520225146105</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.04059547469985</v>
+        <v>10.05377960495311</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.194169567843687</v>
+        <v>9.20756250259106</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.991974981120208</v>
+        <v>9.005423088926676</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.49920309953183</v>
+        <v>12.5126497498168</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.85950798899641</v>
+        <v>14.87306134268191</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.3354475825754</v>
+        <v>12.32501794687725</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.694035895538299</v>
+        <v>0.6827486642669882</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.915308035229089</v>
+        <v>1.928174274099142</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.764911594837422</v>
+        <v>5.777881578019247</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.18976893529782</v>
+        <v>5.20271366689974</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.653720631057624</v>
+        <v>4.666799984847437</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.367323626020436</v>
+        <v>6.380339711224224</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.576417728841797</v>
+        <v>5.589460235250321</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.819491275481028</v>
+        <v>5.8326519697832</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.42653146942086</v>
+        <v>11.43971526990434</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.163877345063852</v>
+        <v>9.177269534965717</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.67051310952138</v>
+        <v>9.683960812019279</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.12531230361927</v>
+        <v>11.13875845509414</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.70843861823301</v>
+        <v>10.72199153851521</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.25211424924223</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>144</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.177927106170777</v>
+        <v>-3.189214626028054</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.016977210608296</v>
+        <v>-2.004118093375801</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.026865324966927</v>
+        <v>-1.013903911285766</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.258454925659059</v>
+        <v>3.271395673041255</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7413184434165956</v>
+        <v>-0.7282452424894785</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2482177311571192</v>
+        <v>0.261228056599748</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.222496889038247</v>
+        <v>-1.209459857056281</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.689280576682116</v>
+        <v>-1.676124900378404</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.137464820611889</v>
+        <v>-3.124287709810773</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.986942543186146</v>
+        <v>-3.973555390433226</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.886332487757386</v>
+        <v>-4.87288888336446</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.241240251702486</v>
+        <v>-6.22779724525688</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.885782146406015</v>
+        <v>-3.872230582613525</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.636774639646823</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>141</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-9.197081264879664</v>
+        <v>-9.208372061591788</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.979454785447935</v>
+        <v>-7.966606281919042</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.961974732725977</v>
+        <v>-6.949022874432387</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.36939487057926</v>
+        <v>-10.35646897146195</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.372592012568091</v>
+        <v>-7.359527183199994</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.955379906250585</v>
+        <v>-4.942375897153774</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.164630026562804</v>
+        <v>-7.151599100528102</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.217208745018276</v>
+        <v>-6.204057598901421</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.155232968460098</v>
+        <v>-4.142058190624127</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.713338457557533</v>
+        <v>-5.699953505790234</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.210835355492854</v>
+        <v>-5.197393068383938</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.469004951812366</v>
+        <v>-4.455562486632566</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.181142846385256</v>
+        <v>-4.167591703972164</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.769162346502618</v>
+        <v>-6.77959198220077</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>144</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.35818711361042</v>
+        <v>2.346913352555838</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6314584611457192</v>
+        <v>-0.6186076606348365</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.74248295298171</v>
+        <v>1.75543852401475</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4890488699646554</v>
+        <v>0.5019796541544963</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.799607431300025</v>
+        <v>4.812678172376195</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.404734184217631</v>
+        <v>4.417741641932359</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.628768084474309</v>
+        <v>3.641802751621782</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.688747729812953</v>
+        <v>-1.675596867387796</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.136909960428333</v>
+        <v>-3.123736924844494</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.986247839366783</v>
+        <v>-3.972864157991864</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.191947253025901</v>
+        <v>-4.178506095990855</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-7.628817552981296</v>
+        <v>-7.61537660853071</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.35679957692701</v>
+        <v>-7.343249192648095</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.108996861868732</v>
+        <v>-7.119426497567197</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>141</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.249094404857921</v>
+        <v>-4.260371411191493</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.030426977429357</v>
+        <v>-3.017584620130208</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-10.49310229959526</v>
+        <v>-10.48016522816035</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.83090504357768</v>
+        <v>-6.817986239037332</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-11.61381588918548</v>
+        <v>-11.6007637650478</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.61373765955883</v>
+        <v>-10.60074559318514</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-10.70137283687377</v>
+        <v>-10.68835124208957</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-10.46296600130308</v>
+        <v>-10.44982343828011</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.110999238371612</v>
+        <v>-9.097831774776523</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.128974698165898</v>
+        <v>-7.115594419516547</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.752841731033328</v>
+        <v>-8.739403577324815</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-10.13863936088217</v>
+        <v>-10.12520010514729</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-9.852861338233751</v>
+        <v>-9.839311792458595</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-6.769162346502938</v>
+        <v>-6.77959198220077</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>144</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7.197432061450023</v>
+        <v>7.186176846063752</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>12.51025370236511</v>
+        <v>12.52311054424602</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.04543582061248</v>
+        <v>10.05839084578133</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.56328198559302</v>
+        <v>11.57621534395066</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.49167356770921</v>
+        <v>14.50474589440444</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>16.17777156170506</v>
+        <v>16.19078244780113</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16.79171520408779</v>
+        <v>16.80475380818851</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>17.71735976537664</v>
+        <v>17.73051738338554</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20.43537088588602</v>
+        <v>20.44855183276242</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>26.5289428891718</v>
+        <v>26.54233592801086</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>24.94592566047662</v>
+        <v>24.95937330562693</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>27.07077308030341</v>
+        <v>27.0842194165097</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>28.04828699832265</v>
+        <v>28.06184017111501</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>29.69655869368667</v>
+        <v>29.68612905798836</v>
       </c>
     </row>
     <row r="14">
@@ -991,98 +991,98 @@
         <v>144</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.174416400754012</v>
+        <v>-3.185679595812161</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7497010448946</v>
+        <v>0.7625365188343025</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.868324519056507</v>
+        <v>-5.855395555782664</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.816156289750353</v>
+        <v>-7.80325067872144</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.202974862864849</v>
+        <v>-4.189926119109543</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.138599992531738</v>
+        <v>-1.125608267832213</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8550571605612021</v>
+        <v>0.8680803019846977</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.933219008657623</v>
+        <v>5.946366622583867</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.874327144440038</v>
+        <v>5.887498345952331</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.414992460442825</v>
+        <v>6.428375392583419</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.294421432064198</v>
+        <v>8.307862694709115</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.332222051143205</v>
+        <v>8.345663702902435</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.915579157980467</v>
+        <v>7.929129835709745</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.168780915908741</v>
+        <v>8.158351280210589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 480.9</t>
+          <t>X ≈ 481</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7174633745464263</v>
+        <v>-0.7287152479488839</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.323131141691924</v>
+        <v>3.335963286645487</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.226937323690137</v>
+        <v>2.239869624445589</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2385290602969619</v>
+        <v>0.2514371029698523</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.114136053037605</v>
+        <v>1.127184470244849</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.246908059524131</v>
+        <v>-4.233925264967588</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.918093140996902</v>
+        <v>-2.905078093357062</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.093140252941353</v>
+        <v>-4.080004026872061</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.863453200964408</v>
+        <v>-4.850291942943265</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-8.546044126923547</v>
+        <v>-8.53267151250671</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.461544301332864</v>
+        <v>-9.44811181240226</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.26478661947871</v>
+        <v>-12.25135160877954</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-12.68876647143472</v>
+        <v>-12.67521912449895</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.15214106990687</v>
+        <v>-13.16257070560502</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>144</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.935507532156016</v>
+        <v>-5.946761061735749</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-10.31091412785239</v>
+        <v>-10.29811547309945</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.39689098930636</v>
+        <v>-11.38399007431321</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.27041058786573</v>
+        <v>-11.25752848174937</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-11.81324341500272</v>
+        <v>-11.80021996387475</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-11.52185858252339</v>
+        <v>-11.50889207909503</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.533418201892609</v>
+        <v>-9.520416367530878</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.38898513948789</v>
+        <v>-11.37586107163231</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.14744957724483</v>
+        <v>-12.13429850121098</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.839970365370519</v>
+        <v>-8.826602043912246</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-8.353762717119452</v>
+        <v>-8.340332878591056</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.322018867101022</v>
+        <v>-8.30858490849203</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-8.050687596206309</v>
+        <v>-8.037140676490196</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-7.108996861869045</v>
+        <v>-7.119426497567197</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>97</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.04239606194885</v>
+        <v>-5.053641036987457</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.651957389615859</v>
+        <v>-6.639164093614951</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-9.097338692651903</v>
+        <v>-9.084445935749869</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.916899225878424</v>
+        <v>-6.904021131358604</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-14.6481912506918</v>
+        <v>-14.63518236805935</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.165805477068986</v>
+        <v>-7.152841988812824</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-12.39372021813519</v>
+        <v>-12.38072909928598</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-11.83656932648106</v>
+        <v>-11.82345231850402</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-12.93130851824025</v>
+        <v>-12.9181636709768</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-13.78485628562485</v>
+        <v>-13.77149543962306</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-18.11323355517455</v>
+        <v>-18.0998117374908</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-18.08577299477471</v>
+        <v>-18.0723443904492</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-22.63492006085198</v>
+        <v>-22.62137662675993</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-21.36300602567203</v>
+        <v>-21.37343566137018</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>96</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.548814583506413</v>
+        <v>-4.56005216190858</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.121672101174759</v>
+        <v>-5.108886114946728</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.366220916671388</v>
+        <v>-1.353323468099347</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.837946815858345</v>
+        <v>0.8508297414198793</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.737019668710083</v>
+        <v>-0.7239981145842904</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4430783401395573</v>
+        <v>-0.4301123140875163</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5105696140906417</v>
+        <v>0.5235699332487371</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.04442320719552129</v>
+        <v>0.05754707282258664</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.062131590367457</v>
+        <v>2.07528491053219</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.904914727504647</v>
+        <v>-1.89154953809475</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.109784055317746</v>
+        <v>-2.096357076726953</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.157577010595638</v>
+        <v>-4.144145732013868</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.620453567884077</v>
+        <v>-5.60690835453358</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.289552417424837</v>
+        <v>-3.29998205312252</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-5.566195107740612</v>
+        <v>-5.105984333016437</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-8.595469926409038</v>
+        <v>-8.986423216681352</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.999611139501219</v>
+        <v>-5.426261437809373</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.371745914583009</v>
+        <v>-4.803076936193023</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.143346466515219</v>
+        <v>-7.554804771827627</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.78565217651003</v>
+        <v>-11.16224065713694</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-13.97971048821718</v>
+        <v>-14.32872268566026</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-11.26955169924999</v>
+        <v>-11.64701901652263</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-11.72668504570127</v>
+        <v>-12.10081143507551</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.620395032031695</v>
+        <v>-8.038760186400445</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.433703394798947</v>
+        <v>-6.864648021189637</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.799980505528268</v>
+        <v>-7.227565134770046</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.819824149886543</v>
+        <v>-6.260020884081044</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.666804669676651</v>
+        <v>-8.210696338837245</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.557268107443861</v>
+        <v>-3.568600779600295</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-11.55182044381237</v>
+        <v>-11.53891063423632</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-14.07434872487721</v>
+        <v>-14.06134159345961</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-13.94409559226987</v>
+        <v>-13.9311164498714</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-14.48251680734188</v>
+        <v>-14.46940600296694</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-16.31273444409414</v>
+        <v>-16.29969154779977</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-20.65278731030259</v>
+        <v>-20.63972105600211</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-20.41075085092838</v>
+        <v>-20.39756984163314</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-22.5994103115786</v>
+        <v>-22.58621157262384</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-24.15875535476272</v>
+        <v>-24.14535022710989</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-24.36350867907998</v>
+        <v>-24.35005138536976</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-28.58444467067088</v>
+        <v>-28.57099238195077</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-29.00469928161562</v>
+        <v>-28.99114323526402</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-28.75497794933949</v>
+        <v>-28.76540758503765</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>144</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.284339457567647</v>
+        <v>0.2730067854112121</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6327897109520109</v>
+        <v>-0.6198799013759597</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.139008249118227</v>
+        <v>3.152015380535829</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.96370582617017</v>
+        <v>3.976684968568634</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.814173499986886</v>
+        <v>4.827284304361825</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.11161543770239</v>
+        <v>5.124658333996756</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.559698321648611</v>
+        <v>4.572879330943849</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.887587324355358</v>
+        <v>5.900786063310122</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.037462139327275</v>
+        <v>5.050867266980106</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.527153259453982</v>
+        <v>5.5406105531642</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.255980861243856</v>
+        <v>6.269433149963966</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.446837361410061</v>
+        <v>4.460393407761664</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>141</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.6849276819121</v>
+        <v>-5.696260354068535</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.587281436720254</v>
+        <v>-6.574371627144203</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.52824943409706</v>
+        <v>-10.51524230267946</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-15.36253530858193</v>
+        <v>-15.34955616618346</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-19.44705581443407</v>
+        <v>-19.43394501005913</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-17.73117416040636</v>
+        <v>-17.718131264112</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-17.81590787767864</v>
+        <v>-17.80284162337816</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-18.99231113461616</v>
+        <v>-18.97913012532092</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-19.05331102079879</v>
+        <v>-19.04011228184402</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-20.61265606398258</v>
+        <v>-20.59925093632975</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-20.8174093883</v>
+        <v>-20.80395209458978</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-24.32912552173455</v>
+        <v>-24.31567323301444</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-25.45859999083564</v>
+        <v>-25.44504394448404</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-26.62731837487125</v>
+        <v>-26.6377480105694</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>144</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.187882764654418</v>
+        <v>-3.199215436810853</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.660567488729868</v>
+        <v>-9.647657679153816</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.583213973104314</v>
+        <v>-6.570206841686712</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.23073861827443</v>
+        <v>-9.217759475875965</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-12.54693761112438</v>
+        <v>-12.53382680674945</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-15.0272734511865</v>
+        <v>-15.01423055489214</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-15.8064516129033</v>
+        <v>-15.79338535860282</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-21.82919056724028</v>
+        <v>-21.81600955794504</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-23.97352378675576</v>
+        <v>-23.96032504780099</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-22.0458711940059</v>
+        <v>-22.03246606635307</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-22.25062451832364</v>
+        <v>-22.23716722461342</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-20.1329080276448</v>
+        <v>-20.11945573892469</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-24.02538486081216</v>
+        <v>-24.01182881446056</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-25.16455241742492</v>
+        <v>-25.17498205312307</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>144</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.756561679790025</v>
+        <v>3.74522900763359</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.533876955714653</v>
+        <v>3.546786765290705</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.222341582451399</v>
+        <v>5.235348713869001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.658150270614456</v>
+        <v>4.67112941301292</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.036395722208951</v>
+        <v>2.04950652658389</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2505043265911979</v>
+        <v>0.2635472228855633</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.249103942652333</v>
+        <v>2.262170196952809</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.865253877204168</v>
+        <v>3.878434886499406</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3320317687997232</v>
+        <v>0.3452305077544864</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.111735629434676</v>
+        <v>-2.098278335724459</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.005980861243934044</v>
+        <v>0.01943314996404411</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9746151391881597</v>
+        <v>0.9881711855397626</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.553441306313331</v>
+        <v>-1.563870942011484</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.440941205132368</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>-0.9006127618960562</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.308391278068697</v>
+        <v>-1.295384146651095</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.305797719929281</v>
+        <v>-3.292818577530817</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.120320072090749</v>
+        <v>1.133430876465688</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.545421584274578</v>
+        <v>3.558464480568944</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.751468008846274</v>
+        <v>2.76453426314675</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.702724326376739</v>
+        <v>3.715905335671977</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.641724440194359</v>
+        <v>3.654923179149122</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.082379397010484</v>
+        <v>2.095784524663316</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4591863563807692</v>
+        <v>0.472643650090987</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.330448946350394</v>
+        <v>3.343901235070504</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.32863405171755</v>
+        <v>4.342190098069153</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.287575242149863</v>
+        <v>5.277145606451711</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>144</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.050784563189147</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.839432511270211</v>
+        <v>2.852342320846262</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.916786026895842</v>
+        <v>5.929793158313444</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.90815027061446</v>
+        <v>10.92112941301293</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.203062388875622</v>
+        <v>6.216173193250562</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10.58243727598568</v>
+        <v>10.59550353028615</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.726364988315275</v>
+        <v>8.739545997610513</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.7486984354663</v>
+        <v>10.76189717442107</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.204128805993946</v>
+        <v>9.217533933646777</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.0827088150097</v>
+        <v>11.09616610871991</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.11709197235513</v>
+        <v>11.13054426107524</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12.3354475825754</v>
+        <v>12.32501794687725</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>-1.440941205132368</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.296501294876357</v>
+        <v>-7.283591485300306</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-9.109809717785005</v>
+        <v>-9.096802586367403</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.851897010709422</v>
+        <v>-6.838917868310958</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.390318225781591</v>
+        <v>-7.377207421406652</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-11.3481954370021</v>
+        <v>-11.33515254070773</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.177610005338209</v>
+        <v>-7.164543751037733</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-9.772452978587793</v>
+        <v>-9.759271969292556</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.287353573989954</v>
+        <v>-6.274154835035191</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-9.265138333485964</v>
+        <v>-9.251733205833133</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.17911151595966</v>
+        <v>-10.16565422224944</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.435508500458113</v>
+        <v>-9.422056211738003</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-11.27420282771507</v>
+        <v>-11.26064678136347</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-11.02448149543886</v>
+        <v>-11.03491113113702</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>144</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.923228346456689</v>
+        <v>7.911895674300254</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.47832140015903</v>
+        <v>10.49123120973508</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.55567491578482</v>
+        <v>13.56868204720242</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16.61972905554229</v>
+        <v>16.63283985991723</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.52828210436905</v>
+        <v>15.54132500066342</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.5268817204301</v>
+        <v>17.53994797473058</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>17.75414276609313</v>
+        <v>17.76732377538837</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>20.47092065768853</v>
+        <v>20.48411939664329</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.70412880599386</v>
+        <v>21.71753393364669</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>22.88826437056532</v>
+        <v>22.90172166427554</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>22.92264752791067</v>
+        <v>22.93609981663078</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>21.80794847252132</v>
+        <v>21.82150451887293</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.97433647146428</v>
+        <v>19.96390683576613</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>144</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.50477099236641</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.144988066825846</v>
+        <v>2.157897876401897</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.833452693562435</v>
+        <v>3.846459824980037</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.047039159503342</v>
+        <v>6.060018301901806</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.438395415472783</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.417170993257947</v>
+        <v>4.430213889552313</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.612007168458774</v>
+        <v>-2.598940914158298</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.3930316549818684</v>
+        <v>0.4062126642771062</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.834634897867026</v>
+        <v>-3.821436158912263</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.379204527339354</v>
+        <v>-5.365799399686523</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.583957851656933</v>
+        <v>-5.570500557946716</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.549574694311545</v>
+        <v>-5.536122405591435</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.580940416367632</v>
+        <v>-4.567384370016029</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.414552417424446</v>
+        <v>-6.424982053122598</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>141</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.371809906740417</v>
+        <v>6.360477234583982</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.46945615193215</v>
+        <v>5.482365961508201</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.620686736115708</v>
+        <v>8.63369386753331</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.460159726879233</v>
+        <v>9.473138869277697</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.921738511807064</v>
+        <v>8.934849316182003</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.219180449522725</v>
+        <v>9.23222334581709</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.843666590406478</v>
+        <v>9.856732844706954</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.667263333468945</v>
+        <v>8.680444342764183</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.478603872818553</v>
+        <v>6.491802611773316</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.465358120414777</v>
+        <v>8.478763248067608</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.09748422872124</v>
+        <v>11.11094152243146</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.96874681869082</v>
+        <v>13.98219910741093</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.548492207746</v>
+        <v>13.5620482540976</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>15.21665325633423</v>
+        <v>15.20622362063607</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>144</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.312117235345504</v>
+        <v>9.300784563189069</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>11.1727658446035</v>
+        <v>11.18567565417955</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.77789713800696</v>
+        <v>10.79090426942457</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>17.15815027061446</v>
+        <v>17.17112941301293</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>17.31417349998672</v>
+        <v>17.32728430436166</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>19.69494877103573</v>
+        <v>19.70799166733009</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.915770609319</v>
+        <v>18.92883686361948</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>19.83747609942639</v>
+        <v>19.85065710872163</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>20.4709206576885</v>
+        <v>20.48411939664327</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>21.0096843615495</v>
+        <v>21.02308948920233</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>23.5827088150097</v>
+        <v>23.59616610871991</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>22.22820308346623</v>
+        <v>22.24165537218634</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>23.89128180585467</v>
+        <v>23.90483785220627</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>23.44655869368647</v>
+        <v>23.43612905798832</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>141</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.790249623052482</v>
+        <v>7.778916950896047</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.306335584556308</v>
+        <v>8.319245394132359</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.29444560136393</v>
+        <v>14.30745273278153</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>13.00625901765937</v>
+        <v>13.01923816005783</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.88627751889923</v>
+        <v>13.89938832327417</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.93586517196676</v>
+        <v>16.94893142626724</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>16.46868177318526</v>
+        <v>16.4818627824805</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>20.66300103593917</v>
+        <v>20.67619977489393</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.35897514169135</v>
+        <v>23.37238026934418</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>24.5726615336858</v>
+        <v>24.58611882739602</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>26.0254844073433</v>
+        <v>26.03893669606341</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>27.02366951271046</v>
+        <v>27.03722555906207</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>29.4010504194548</v>
+        <v>29.39062078375665</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2843394575678033</v>
+        <v>0.2730067854113685</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.06165473349243911</v>
+        <v>0.07456454306849025</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.110991750881936</v>
+        <v>-3.097984619464334</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.980738618274437</v>
+        <v>-2.967759475875972</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.036395722208972</v>
+        <v>2.049506526583912</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.832829006742053</v>
+        <v>-1.819786110447687</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.223118279569889</v>
+        <v>-1.210052025269412</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3014127894624963</v>
+        <v>-0.2882317801672585</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.954128805993939</v>
+        <v>2.96753393364677</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6660421483430241</v>
+        <v>0.6794994420532419</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.363504028076889</v>
+        <v>2.377060074428492</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.918780915908748</v>
+        <v>1.908351280210596</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>137</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.508036860355958</v>
+        <v>-6.519369532512393</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.740048429524613</v>
+        <v>-3.727138619948562</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.864844143420456</v>
+        <v>-4.851837012002854</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.924372032710771</v>
+        <v>-6.911392890312307</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.002939233184392</v>
+        <v>-5.989828428809453</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.625205324665814</v>
+        <v>-8.612162428371448</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.709939041938092</v>
+        <v>-8.696872787637616</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-10.63697645531813</v>
+        <v>-10.6237954460229</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.61768437069752</v>
+        <v>-13.60448563174275</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-15.19773656302471</v>
+        <v>-15.18433143537188</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-13.94263587274376</v>
+        <v>-13.92917857903354</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-15.36810672999686</v>
+        <v>-15.35465444127675</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-16.51828834824104</v>
+        <v>-16.50473230188943</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.88900497216913</v>
+        <v>-11.89943460786728</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days To Halving is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days To Halving is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,105 +2210,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 28.82</t>
+          <t>X &gt; 28.84</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07074535697646667</v>
+        <v>-0.07049640619308661</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0865024348790584</v>
+        <v>-0.0867454155387648</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1515249759462236</v>
+        <v>-0.1517541707984265</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.0567620100872972</v>
+        <v>-0.05701377280383468</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1432424828984225</v>
+        <v>-0.1434759295564589</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07623330816683449</v>
+        <v>-0.07648175320230877</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.02302087348221704</v>
+        <v>0.02274769302518109</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.05698829454834708</v>
+        <v>0.05670441425686334</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.05825225618139029</v>
+        <v>0.05796763512568504</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1244964650146017</v>
+        <v>0.1241913839734039</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1287248701177646</v>
+        <v>0.1284176135190052</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1280511737440122</v>
+        <v>0.1277441092025882</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.161123075695933</v>
+        <v>0.1608057341507134</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1560386915153131</v>
+        <v>0.156214528073825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 76.41</t>
+          <t>X &gt; 76.43</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3359818478405643</v>
+        <v>-0.335245260782159</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3442850275710043</v>
+        <v>-0.3449408821144573</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3973812709245763</v>
+        <v>-0.3980294901805763</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3292234667592808</v>
+        <v>-0.3298874458049994</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5256289192549417</v>
+        <v>-0.5262510491736876</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4165693918972906</v>
+        <v>-0.4172153153535234</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4117923592598842</v>
+        <v>-0.4124409983759136</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4102488752955438</v>
+        <v>-0.4109046805126439</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3562671495877723</v>
+        <v>-0.3569377879427051</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2820455322289561</v>
+        <v>-0.2827470046872662</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3967933914720234</v>
+        <v>-0.3974690286936777</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3988774383511355</v>
+        <v>-0.3995524306075922</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3494167514725888</v>
+        <v>-0.3501104158998984</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3892359617283958</v>
+        <v>-0.3885355838744644</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4379264060963379</v>
+        <v>-0.4367081651412832</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5429375486797383</v>
+        <v>-0.5440528960517028</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.5307949703969683</v>
+        <v>-0.531923272627715</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3339880941654201</v>
+        <v>-0.3351655248382102</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5174851573599994</v>
+        <v>-0.5186276453238676</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4941935700468392</v>
+        <v>-0.4953358410432855</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6696389544540509</v>
+        <v>-0.6707378028141378</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.8340873843091785</v>
+        <v>-0.83515458810502</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.7496324196606636</v>
+        <v>-0.7507237886196165</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6405781056421063</v>
+        <v>-0.6417185226930684</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7520174181807064</v>
+        <v>-0.7531339787691493</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.8868762816131266</v>
+        <v>-0.8879572412146644</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.9248463790678443</v>
+        <v>-0.9259277873828964</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.8706743301939071</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4814752968277105</v>
+        <v>-0.4797641970415967</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6375112532721445</v>
+        <v>-0.6391385564421199</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.7730035995096642</v>
+        <v>-0.7746080745756814</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5464982554626374</v>
+        <v>-0.5481608783665948</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.716431955768428</v>
+        <v>-0.7180671695612304</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.758170084274802</v>
+        <v>-0.7597849007458777</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9099374516831702</v>
+        <v>-0.9115146504320109</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.090064080361138</v>
+        <v>-1.091608686485344</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.218074195475261</v>
+        <v>-1.219586829332066</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.017775436760672</v>
+        <v>-1.0193719095261</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.15299335389858</v>
+        <v>-1.154560701491775</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.349009594169132</v>
+        <v>-1.35052322953424</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.372402500382833</v>
+        <v>-1.373924684532817</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.298590616606042</v>
+        <v>-1.296776924917623</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3711972336225386</v>
+        <v>-0.3689859852942803</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5810945824807732</v>
+        <v>-0.5833301937736195</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7626212966224628</v>
+        <v>-0.7648242584239853</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7021112228246125</v>
+        <v>-0.7043267339607766</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7154141613289724</v>
+        <v>-0.7176510302932897</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7993288020885458</v>
+        <v>-0.8015298938911855</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8971545607490228</v>
+        <v>-0.8993329043349334</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.065557640295751</v>
+        <v>-1.067710238217146</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.139575970533571</v>
+        <v>-1.141711495206877</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8963440072448279</v>
+        <v>-0.8985875764055393</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.000309220051477</v>
+        <v>-1.002533654873474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.148929726323402</v>
+        <v>-1.151111685450175</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.269611625907586</v>
+        <v>-1.271779298580626</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.202964800270379</v>
+        <v>-1.200677680607136</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.003016864271280895</v>
+        <v>-0.0003514284300578652</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2724647633629118</v>
+        <v>-0.2754207207098816</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5040092154122249</v>
+        <v>-0.5069206781645406</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2988310469863293</v>
+        <v>-0.3017972883862043</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4377034876530175</v>
+        <v>-0.4406606317248674</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6259550725953957</v>
+        <v>-0.6288415512529042</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6357007025597454</v>
+        <v>-0.6385906583535004</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8506514847437217</v>
+        <v>-0.8535058673634026</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.013774894584571</v>
+        <v>-1.016586122815916</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.695398380767287</v>
+        <v>-0.6983531498917159</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8246630114428299</v>
+        <v>-0.8275927565283183</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.010429546798569</v>
+        <v>-1.013304065525091</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.148154258426118</v>
+        <v>-1.15101338637708</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.9707654351760766</v>
+        <v>-0.9680166582691569</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1080889819520507</v>
+        <v>-0.1047709923664044</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2564897656865455</v>
+        <v>-0.2601538318160976</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6039767284680764</v>
+        <v>-0.6075631635256258</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3338912163438508</v>
+        <v>-0.3375538159505638</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6707605866422739</v>
+        <v>-0.6743587434920997</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8498176353213154</v>
+        <v>-0.8533420084103653</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8254669279407452</v>
+        <v>-0.8290066765915114</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8133567198209875</v>
+        <v>-0.8169346273252458</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9192966963517151</v>
+        <v>-0.9228481816691385</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5489576137591499</v>
+        <v>-0.5526844488826228</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.6748209438322021</v>
+        <v>-0.6785252493047764</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7159153709981112</v>
+        <v>-0.7196066771430125</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8718733789872672</v>
+        <v>-0.8755478454122851</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6976179304035952</v>
+        <v>-0.6943672863634092</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.0805642537926019</v>
+        <v>0.08448600345217727</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1301165356846923</v>
+        <v>-0.1345731660692238</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1534543680386946</v>
+        <v>-0.1579388446905199</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.03790447978812495</v>
+        <v>-0.04241784319371078</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1722239799674483</v>
+        <v>-0.1767414605336555</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4049993078843244</v>
+        <v>-0.4094195583285654</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3755468202963002</v>
+        <v>-0.3799861392093291</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3737460869650988</v>
+        <v>-0.378227481865089</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5461044319172075</v>
+        <v>-0.5505378823706408</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2491894687183347</v>
+        <v>-0.2537922312277772</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3068077189548717</v>
+        <v>-0.3114116045209201</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.286641030909685</v>
+        <v>-0.2912511624955272</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4627233621039935</v>
+        <v>-0.4673144098394388</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4210144529657924</v>
+        <v>-0.4172301151382598</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2667176724366911</v>
+        <v>-0.2619379400898509</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.7469289092120306</v>
+        <v>-0.7520211519382585</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6511297957465132</v>
+        <v>-0.6562963905671921</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6040077840967939</v>
+        <v>-0.6091804376885577</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8877784519652252</v>
+        <v>-0.8929115754086823</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.214189075834469</v>
+        <v>-1.219185509847087</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.213258013624426</v>
+        <v>-1.218266136643372</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.256538104158324</v>
+        <v>-1.261580889926101</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.569937859827633</v>
+        <v>-1.574883722133237</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.555882474321912</v>
+        <v>-1.560920434117477</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.53906580321042</v>
+        <v>-1.544132819650081</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.62160125863408</v>
+        <v>-1.626639971227483</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.853975646719867</v>
+        <v>-1.858980486959176</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.890662210715014</v>
+        <v>-1.885686660168822</v>
       </c>
     </row>
     <row r="15">
@@ -2682,101 +2682,101 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1175517953872856</v>
+        <v>-0.1120024705656277</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.8237065057176807</v>
+        <v>-0.8296907760804473</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3834860336671966</v>
+        <v>-0.3896759205561366</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2340222533471987</v>
+        <v>-0.2402537586612326</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7177078131445853</v>
+        <v>-0.7238339065009498</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.218066820043802</v>
+        <v>-1.223984342770926</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.319363245217843</v>
+        <v>-1.325258261701222</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.625374949276072</v>
+        <v>-1.63121922390097</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.951831041378959</v>
+        <v>-1.957569982035061</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.964790914153099</v>
+        <v>-1.970627912409817</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.043526851261561</v>
+        <v>-2.049363358847984</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.1322355858902</v>
+        <v>-2.138040159644412</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.355156940584081</v>
+        <v>-2.360934862480647</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.40671486843992</v>
+        <v>-2.400765528906227</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 504.7</t>
+          <t>X &gt; 504.8</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08582353857504188</v>
+        <v>-0.07939785803805677</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.043025376042046</v>
+        <v>-1.049922205718374</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.521546683850012</v>
+        <v>-0.5286957637677077</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.259014652155841</v>
+        <v>-0.2662486636068522</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8145907783102544</v>
+        <v>-0.8216942706258692</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.057876791999263</v>
+        <v>-1.064853607851639</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.234809263483093</v>
+        <v>-1.24173572841908</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.494859229914923</v>
+        <v>-1.501755910358057</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.797840522061044</v>
+        <v>-1.80463642504666</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.616720132832526</v>
+        <v>-1.623703222640927</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.651201097150505</v>
+        <v>-1.658203429357485</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.596342976836944</v>
+        <v>-1.603365651084964</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.80863070508147</v>
+        <v>-1.815635244578672</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.838408381415604</v>
+        <v>-1.831806200104381</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2481790367919956</v>
+        <v>0.2554813735641943</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5138517121797577</v>
+        <v>-0.5220823997322981</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.09940874041078018</v>
+        <v>0.09086919093643786</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3697089857276765</v>
+        <v>0.3610776518162666</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1865947514729456</v>
+        <v>-0.1950958957436484</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4604091560613313</v>
+        <v>-0.4687610435000522</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7609790941210903</v>
+        <v>-0.7692307692307665</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9299289638647537</v>
+        <v>-0.9381922388465753</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.206903288140957</v>
+        <v>-1.215071883244185</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.204290301950103</v>
+        <v>-1.212598414768131</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.268501306002406</v>
+        <v>-1.276821486951768</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.212323417678334</v>
+        <v>-1.220665859936865</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.452224601861019</v>
+        <v>-1.460543376883365</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.537470736219205</v>
+        <v>-1.530015743174275</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4598020407416286</v>
+        <v>0.4677587329308466</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2683274850823096</v>
+        <v>-0.277499990702367</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4672786377332869</v>
+        <v>0.4577305129844831</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6611733141919203</v>
+        <v>0.6515618158591181</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3918691084958112</v>
+        <v>0.3822694743365744</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1921933032210177</v>
+        <v>-0.2015080131227549</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2956694491605276</v>
+        <v>-0.3049622869490918</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4936633493601192</v>
+        <v>-0.5029613123310028</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7379270789369841</v>
+        <v>-0.7471411728525652</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7010676626031014</v>
+        <v>-0.7104496054478844</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5947120160355155</v>
+        <v>-0.6041792551701235</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5373854345944764</v>
+        <v>-0.5468765699699745</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6049167835013876</v>
+        <v>-0.6144589476838505</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.7444493246410957</v>
+        <v>-0.736606125670157</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6662542502426234</v>
+        <v>0.6749131732332501</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.06827549575432812</v>
+        <v>-0.07843858815839155</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5428544029642239</v>
+        <v>0.5323490461106886</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6538868151966568</v>
+        <v>0.6433516352351489</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4384012349929165</v>
+        <v>0.4278495981719388</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1818519706558988</v>
+        <v>-0.1920891234692661</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3289021456277297</v>
+        <v>-0.339099236794155</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5158429583894559</v>
+        <v>-0.5260552200454924</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.853343838169792</v>
+        <v>-0.8634299728546821</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6514457999021417</v>
+        <v>-0.6617862605834546</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.532261644300398</v>
+        <v>-0.542698967243318</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3881632829001376</v>
+        <v>-0.3986629049243859</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3981793291000386</v>
+        <v>-0.4087614613930484</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6395416832039018</v>
+        <v>-0.630990636813749</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2218</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9781577122517007</v>
+        <v>0.9668250400952658</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3584686799907857</v>
+        <v>0.3713784895668368</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8202275658197991</v>
+        <v>0.8332346972374012</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9053950356680502</v>
+        <v>0.9183741780665144</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8178304481883174</v>
+        <v>0.8309412525632567</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3488161189968579</v>
+        <v>0.3618590152912233</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3542537272430621</v>
+        <v>0.3673199815435382</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.02232731673927901</v>
+        <v>0.03550832603451681</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3091865459984717</v>
+        <v>-0.2959878070437085</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3026841386007959</v>
+        <v>-0.2892790109479648</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2369234863629188</v>
+        <v>-0.2234661926527011</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.06728334073975617</v>
+        <v>-0.05383105201964611</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1268526496107185</v>
+        <v>-0.1132966032591156</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2378166194083704</v>
+        <v>-0.2482462551065225</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2077</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.286051328321555</v>
+        <v>1.27471865616512</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.167015028790139</v>
+        <v>1.17992483836619</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.831366351081371</v>
+        <v>1.844373482498973</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.913473118739425</v>
+        <v>1.926452261137889</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.856515553161721</v>
+        <v>1.86962635753666</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.479908381585126</v>
+        <v>1.492951277879492</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.780345583908421</v>
+        <v>1.793411838208897</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.409454915025812</v>
+        <v>1.42263592432105</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.204015933995173</v>
+        <v>1.217214672949936</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.316818047956168</v>
+        <v>1.330223175608999</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.400942913335264</v>
+        <v>1.414400207045482</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.868643355225714</v>
+        <v>1.882095643945824</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.833559663876379</v>
+        <v>1.847115710227982</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.6981100765571</v>
+        <v>1.687680440858948</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1933</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.360674457855211</v>
+        <v>1.349341785698776</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.301092567601764</v>
+        <v>1.314002377177815</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.733952779784268</v>
+        <v>1.74695991120187</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.760739797544382</v>
+        <v>1.773718939942846</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.63618304186177</v>
+        <v>1.649293846236709</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.209362175645715</v>
+        <v>1.222405071940081</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.641959032610373</v>
+        <v>1.655025286910849</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.174775633828872</v>
+        <v>1.18795664312411</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8551104605280955</v>
+        <v>0.8683091994828587</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.039646423974048</v>
+        <v>1.053051551626879</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.093558386774937</v>
+        <v>1.107015680485155</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.541806003509926</v>
+        <v>1.555258292230036</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.638881966801954</v>
+        <v>1.652438013153557</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.681671069383469</v>
+        <v>1.671241433685317</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1792</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.915043822647164</v>
+        <v>1.903711150490729</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.921773781111476</v>
+        <v>1.934683590687527</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.698780074514886</v>
+        <v>2.711787205932488</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.108051064265247</v>
+        <v>3.121030206663711</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.295076277764508</v>
+        <v>3.308187082139447</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.69966107262303</v>
+        <v>2.712703968917396</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.172963069636459</v>
+        <v>3.186029323936935</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.761583242283528</v>
+        <v>2.774764251578766</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.42156549895838</v>
+        <v>2.434764237913143</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.743315313930452</v>
+        <v>2.756720441583283</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.81757984675572</v>
+        <v>2.831037140465938</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.577409432672582</v>
+        <v>3.590861721392692</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.770994107441972</v>
+        <v>3.784550153793575</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.909108296861106</v>
+        <v>3.898678661162954</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1648</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.360930611828856</v>
+        <v>2.349597939672421</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.933823018282077</v>
+        <v>2.946732827858128</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.509828098093251</v>
+        <v>3.522835229510854</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.186197735555126</v>
+        <v>4.19917687795359</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.679329918541207</v>
+        <v>4.692440722916146</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.248616516451044</v>
+        <v>4.261659412745409</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.83135852733411</v>
+        <v>4.844424781634586</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.91029163340697</v>
+        <v>4.923472642702208</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.727932523923698</v>
+        <v>4.741131262878461</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.909360736954028</v>
+        <v>4.922765864606859</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.008005470888875</v>
+        <v>5.021462764599093</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.649184744739152</v>
+        <v>5.662637033459262</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.199803920202029</v>
+        <v>6.213359966553632</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.449525252478317</v>
+        <v>6.439095616780165</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1504</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.227306360641087</v>
+        <v>2.215973688484652</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.87637104554917</v>
+        <v>2.889280855125222</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.34586404108024</v>
+        <v>3.358871172497842</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.141010790709018</v>
+        <v>4.153989933107482</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.932376809679404</v>
+        <v>4.945487614054343</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.631414492075919</v>
+        <v>4.644457388370284</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.078595668420661</v>
+        <v>5.091661922721137</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.010348439851924</v>
+        <v>5.023529449147162</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.148816638775997</v>
+        <v>5.162015377730761</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.362521240982119</v>
+        <v>5.37592636863495</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.689682810281553</v>
+        <v>5.703140103991771</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.189491499541887</v>
+        <v>6.202943788261997</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.70008795242677</v>
+        <v>6.713643998778373</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.215766731511565</v>
+        <v>7.205337095813412</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1363</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.605607901360095</v>
+        <v>2.59427522920366</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.268429005930685</v>
+        <v>3.281338815506736</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.827338729268064</v>
+        <v>3.840345860685666</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.911370291809533</v>
+        <v>4.924349434207997</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.326727506671332</v>
+        <v>5.339838311046272</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.743758585986406</v>
+        <v>4.756801482280771</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.319333012514562</v>
+        <v>5.332399266815038</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.145619899866595</v>
+        <v>5.158800909161833</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.304722728284439</v>
+        <v>5.317921467239202</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.701846259324007</v>
+        <v>5.715251386976838</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.230768650340252</v>
+        <v>6.24422594405047</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.485254522285828</v>
+        <v>6.498706811005938</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.945410769741521</v>
+        <v>6.958966816093124</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.415234816617954</v>
+        <v>7.404805180919801</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1219</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.551680629749008</v>
+        <v>2.540347957592573</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.31910619644021</v>
+        <v>3.332016006016261</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.580513125610636</v>
+        <v>3.593520257028239</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.202972985043402</v>
+        <v>4.215952127441867</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.22320640491791</v>
+        <v>5.236317209292849</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.372165980041288</v>
+        <v>4.385208876335653</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.697604535123389</v>
+        <v>4.710670789423865</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.722627863167162</v>
+        <v>4.7358088724624</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.66162797698486</v>
+        <v>4.674826715939624</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.288122972432731</v>
+        <v>5.301528100085562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.657610829411297</v>
+        <v>5.671068123121515</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.938097350169365</v>
+        <v>5.951549638889475</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.338187283933237</v>
+        <v>6.35174333028484</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.834011979622154</v>
+        <v>6.823582343924002</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1078</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.072424388509873</v>
+        <v>3.061091716353438</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.707604022298867</v>
+        <v>4.720513831874918</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.240379100488916</v>
+        <v>5.253386231906518</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.64892536853241</v>
+        <v>5.661904510930874</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.873027344554863</v>
+        <v>6.886138148929803</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.428354254441203</v>
+        <v>6.441397150735568</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.250856158690269</v>
+        <v>6.263922412990745</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.618552166216745</v>
+        <v>6.631733175511982</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.093730387641116</v>
+        <v>6.10692912659588</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.191657150665144</v>
+        <v>7.205062278317975</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.729018854176886</v>
+        <v>7.742476147887103</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.948930768479627</v>
+        <v>7.962383057199737</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.641848699278704</v>
+        <v>8.655404745630307</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.169863166990993</v>
+        <v>9.159433531292841</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>934</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.324548831824288</v>
+        <v>2.313216159667853</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.817900272393224</v>
+        <v>3.830810081969275</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.95836347157821</v>
+        <v>3.971370602995812</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.623948509967299</v>
+        <v>4.636927652365763</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.370323868770932</v>
+        <v>5.383434673145871</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.025367519548688</v>
+        <v>5.038410415843053</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.512368277651149</v>
+        <v>4.525434531951625</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.901715928120176</v>
+        <v>4.914896937415413</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.877118611531024</v>
+        <v>3.890317350485788</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.954188287316811</v>
+        <v>4.967593414969642</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.391833249937122</v>
+        <v>5.40529054364734</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.64034916959519</v>
+        <v>5.6538014583153</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.611957513682405</v>
+        <v>6.625513560034008</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.504077132896604</v>
+        <v>7.493647497198452</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>790</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.202764211435593</v>
+        <v>3.191431539279158</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.122836168091588</v>
+        <v>4.135745977667639</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.981132018457025</v>
+        <v>3.994139149874627</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.364549708026551</v>
+        <v>4.377528850425016</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.724862670169571</v>
+        <v>5.737973474544511</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.136228658518142</v>
+        <v>5.149271554812508</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.810988612131943</v>
+        <v>5.824054866432419</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.723552048793479</v>
+        <v>5.736733058088717</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.282805327168141</v>
+        <v>5.296004066122904</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.837743433279456</v>
+        <v>6.851148560932288</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.392483779847943</v>
+        <v>7.405941073558161</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.680031494155401</v>
+        <v>7.693483782875511</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.652181946501649</v>
+        <v>8.665737992853252</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.04114378510704</v>
+        <v>10.03071414940889</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>649</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.514265840036551</v>
+        <v>2.502933167880116</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.830273120754889</v>
+        <v>3.84318293033094</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.973154799366313</v>
+        <v>2.986161930783915</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.257491136904477</v>
+        <v>3.270470279302941</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.030317995792245</v>
+        <v>5.043428800167185</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.249177498993262</v>
+        <v>4.262220395287628</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.934859806374305</v>
+        <v>4.947926060674781</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.084009227315448</v>
+        <v>5.097190236610686</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.023009341133147</v>
+        <v>5.03620808008791</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.484132230065157</v>
+        <v>6.497537357717988</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.587545315608907</v>
+        <v>6.601002609319124</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.313762063093009</v>
+        <v>6.327214351813119</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.588422706385394</v>
+        <v>7.601978752736997</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.916726473176311</v>
+        <v>8.906296837478159</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>505</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.5758686104830986</v>
+        <v>0.5645359383266637</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.736572225241616</v>
+        <v>1.749482034817667</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7476441127044282</v>
+        <v>0.7606512441220303</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7062611705296575</v>
+        <v>-0.6932820281311933</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.527594842120941</v>
+        <v>1.54070564649588</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1551612399653735</v>
+        <v>-0.1421183436710081</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.9482238546435369</v>
+        <v>0.9612901089440129</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.8770800598224326</v>
+        <v>0.8902610691176704</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6180603716599364</v>
+        <v>0.6312591106146996</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.342192612374575</v>
+        <v>2.355597740027406</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.741399684096599</v>
+        <v>1.754856977806817</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.77578284144203</v>
+        <v>1.78923513016214</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.939686646338714</v>
+        <v>2.953242692690317</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.773566394456587</v>
+        <v>4.763136758758435</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>364</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.218713045484705</v>
+        <v>-2.23004571764114</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.8083086364709331</v>
+        <v>-0.7953988268948819</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.017979155514972</v>
+        <v>-6.005000013116508</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.259697073883835</v>
+        <v>-3.246586269508896</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.885332059245101</v>
+        <v>-4.872289162950736</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.244791051242657</v>
+        <v>-5.231724796942181</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.146600709832832</v>
+        <v>-7.133401970878069</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.798923697058569</v>
+        <v>-5.785518569405738</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.102578120277244</v>
+        <v>-7.089120826567026</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-7.61764551238236</v>
+        <v>-7.60419322366225</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.389548474975619</v>
+        <v>-6.375992428624016</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.766200769072945</v>
+        <v>-4.776630404771097</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>220</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.857074683846335</v>
+        <v>-3.86840735600277</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.377739205901513</v>
+        <v>-1.364829396325462</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-5.408971548861729</v>
+        <v>-5.395964417444127</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-8.005991143526963</v>
+        <v>-7.993012001128498</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.726230540417312</v>
+        <v>-6.713119736042373</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.883334057247104</v>
+        <v>-6.870291160952739</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.87715868361029</v>
+        <v>-7.864092429309814</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.34434208239179</v>
+        <v>-8.331161073096553</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.04170560493773</v>
+        <v>-12.02850686598297</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.52819442632929</v>
+        <v>-11.51478929867646</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-12.18749320519233</v>
+        <v>-12.17403591148211</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-12.60765550239235</v>
+        <v>-12.59420321367224</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.11881920424634</v>
+        <v>-12.10526315789474</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.141825144697329</v>
+        <v>-9.152254780395481</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.5186098725611146</v>
+        <v>0.5072772004046797</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.521494090922161</v>
+        <v>2.534403900498212</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.30710955543347</v>
+        <v>-6.294102424015868</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-9.791314254151274</v>
+        <v>-9.77833511175281</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.920096915006575</v>
+        <v>-7.906986110631635</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.008197145965617</v>
+        <v>-3.995154249671252</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-6.502569417454758</v>
+        <v>-6.489503163154282</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-4.560114262019397</v>
+        <v>-4.546933252724159</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.440391256635429</v>
+        <v>-9.427192517680666</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.471239333229626</v>
+        <v>-5.457834205576795</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-9.290450488872501</v>
+        <v>-9.276993195162284</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.051248054418636</v>
+        <v>-8.037795765698526</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.857044834038241</v>
+        <v>-4.843488787686638</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.607323501761954</v>
+        <v>-4.617753137460106</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Days To Halving is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Days To Halving is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,105 +3904,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 28.82</t>
+          <t>X &lt; 28.84</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.447609960014546</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.781571519621224</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.842571405803525</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.854749940177079</v>
+        <v>-7.841193893825476</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.605028607900792</v>
+        <v>-7.615458243598944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 76.41</t>
+          <t>X &lt; 76.43</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>228</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.828562340966926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.982707365071377</v>
+        <v>5.995617174647428</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.903628132159007</v>
+        <v>6.916635263576609</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.718091791082287</v>
+        <v>5.731070933480751</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.127038997062755</v>
+        <v>9.140149801437694</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.231498478638066</v>
+        <v>7.244541374932432</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.146764761365787</v>
+        <v>7.159831015666263</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.118177853812362</v>
+        <v>7.1313588631076</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.179984985173917</v>
+        <v>6.19318372412868</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.891263308917914</v>
+        <v>4.904668436570745</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.879492440740684</v>
+        <v>6.892949734450902</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.055024495913138</v>
+        <v>6.068580542264741</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.743342319417501</v>
+        <v>6.732912683719348</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>372</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.495808991617984</v>
+        <v>4.48447631946155</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.572407421664479</v>
+        <v>5.585317231240531</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.446355919368962</v>
+        <v>5.459363050786564</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.426071417567861</v>
+        <v>3.439050559966326</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.307005041205372</v>
+        <v>5.320115845580311</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.066812570318881</v>
+        <v>5.079855466613246</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.86379928315413</v>
+        <v>6.876865537454606</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.547153518781229</v>
+        <v>8.560334528076467</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.679702019695704</v>
+        <v>7.692900758650467</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.560759630366697</v>
+        <v>6.574164758019528</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.700092327554493</v>
+        <v>7.713549621264711</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.078561506405293</v>
+        <v>9.092013795125403</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.464758508363623</v>
+        <v>9.478314554715226</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.908028227736679</v>
+        <v>8.897598592038527</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>513</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.45198078310387</v>
+        <v>3.440648110947436</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.569452004447605</v>
+        <v>4.582361814023656</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.539105715005</v>
+        <v>5.552112846422602</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.914972882700226</v>
+        <v>3.927952025098691</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.130937632540331</v>
+        <v>5.14404843691527</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.428379570255991</v>
+        <v>5.441422466550357</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.513236496258571</v>
+        <v>6.526302750559047</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.800439062389351</v>
+        <v>7.813620071684589</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.714098045602761</v>
+        <v>8.727296784557524</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.279177538937411</v>
+        <v>7.292582666590242</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.244014857894683</v>
+        <v>8.257472151604901</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.642920432394106</v>
+        <v>9.656372721114217</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.807461143086634</v>
+        <v>9.821017189438237</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.277455379846359</v>
+        <v>9.267025744148206</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>657</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.996668224691085</v>
+        <v>1.98533555253465</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.124820639124088</v>
+        <v>3.13773044870014</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.099814946226132</v>
+        <v>4.112822077643735</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.773447074267423</v>
+        <v>3.786426216665888</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.843853865283528</v>
+        <v>3.856964669658467</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.293502804521268</v>
+        <v>4.306545700815633</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.81759709333727</v>
+        <v>4.830663347637746</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.720276708254396</v>
+        <v>5.733457717549634</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.115897826638303</v>
+        <v>6.129096565593066</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.809151637044167</v>
+        <v>4.822556764696998</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>5.36543332033694</v>
+        <v>5.378890614047158</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.160851485292717</v>
+        <v>6.174303774012827</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.806045885002312</v>
+        <v>6.819601931353915</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.446939211190319</v>
+        <v>6.436509575492167</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>798</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01282734395042695</v>
+        <v>0.001494671793992097</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.158145961562617</v>
+        <v>1.171055771138668</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.14172337025424</v>
+        <v>2.154730501671843</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.269470237197574</v>
+        <v>1.282449379596038</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.858868570997593</v>
+        <v>1.871979375372533</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.657563641545337</v>
+        <v>2.670606537839703</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.698143207481074</v>
+        <v>2.71120946178155</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.609405923987801</v>
+        <v>3.622586933283038</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.948907419193603</v>
+        <v>2.962312546846434</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.496033794124152</v>
+        <v>3.50949108783437</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.282296650717697</v>
+        <v>4.295748939437807</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.864548305436955</v>
+        <v>4.878104351788558</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.111763372049083</v>
+        <v>4.101333736350931</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>942</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3728037180065868</v>
+        <v>0.361471045850152</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8843723555731131</v>
+        <v>0.8972821651491643</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.081860336874612</v>
+        <v>2.094867468292215</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.150542344216717</v>
+        <v>1.163521486615181</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.310634929569176</v>
+        <v>2.323745733944115</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.926548204864453</v>
+        <v>2.939591101158818</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.841814487592174</v>
+        <v>2.85488074189265</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.799259538916836</v>
+        <v>2.812440548212074</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.162888102840689</v>
+        <v>3.176086841795453</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.888134467706607</v>
+        <v>1.901539595359438</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.32032381854826</v>
+        <v>2.333781112258478</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.46086408842023</v>
+        <v>2.47431637714034</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.996023490214185</v>
+        <v>3.009579536565788</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.396487922278155</v>
+        <v>2.386058286580003</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1083</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2312037865072938</v>
+        <v>-0.2425364586637286</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3732890825229092</v>
+        <v>0.3861988920989603</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4401008930084913</v>
+        <v>0.4531080244260934</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1086735085338191</v>
+        <v>0.1216526509322833</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.493613327626008</v>
+        <v>0.5067241320009472</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.160399679007412</v>
+        <v>1.173442575301777</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.075665961735133</v>
+        <v>1.088732216035609</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.070163080035805</v>
+        <v>1.083344089331042</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.563179814352125</v>
+        <v>1.576378553306888</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7130546293241977</v>
+        <v>0.7264597569770288</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8776457186723547</v>
+        <v>0.8911030123825725</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.8196927726013499</v>
+        <v>0.8331450613214599</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.322799195820814</v>
+        <v>1.336355242172417</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.203176114431358</v>
+        <v>1.192746478733206</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1227</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6442959911184687</v>
+        <v>0.6329633189620338</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.803708523223484</v>
+        <v>1.816618332799536</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.571839001630977</v>
+        <v>1.584846133048579</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.457593356732353</v>
+        <v>1.470572499130817</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.141666029190745</v>
+        <v>2.154776833565684</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.928105521918638</v>
+        <v>2.941148418213004</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.924871397148401</v>
+        <v>2.937937651448877</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.02818514588116</v>
+        <v>3.041366155176398</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.782181184719235</v>
+        <v>3.795379923673998</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.747051924711677</v>
+        <v>3.760457052364508</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.705297785398173</v>
+        <v>3.718755079108391</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.902680127747679</v>
+        <v>3.916132416467789</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.460420626827229</v>
+        <v>4.473976673178832</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.547142774099441</v>
+        <v>4.536713138401289</v>
       </c>
     </row>
     <row r="15">
@@ -4379,98 +4379,98 @@
         <v>1371</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.241791439089809</v>
+        <v>0.2304587669333742</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.693675156541303</v>
+        <v>1.706584966117354</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7882302282087537</v>
+        <v>0.8012373596263558</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.480846599328288</v>
+        <v>0.4938257417267522</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.474154049463991</v>
+        <v>1.48726485383893</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.500990589659601</v>
+        <v>2.514033485953966</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.708014713379292</v>
+        <v>2.721080967679768</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.334923218317712</v>
+        <v>3.34810422761295</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.003317934615346</v>
+        <v>4.016516673570109</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.02846627256335</v>
+        <v>4.041871400216181</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.188410249485749</v>
+        <v>4.201867543195966</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.368672327327161</v>
+        <v>4.382124616047271</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.823691239358197</v>
+        <v>4.8372472857098</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.927533651138496</v>
+        <v>4.917104015440344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 504.7</t>
+          <t>X &lt; 504.8</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1512</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1520643252926774</v>
+        <v>0.1407316531362426</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9233997835095948</v>
+        <v>0.936406914927197</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4584148208790069</v>
+        <v>0.4713939632774711</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.441157626970856</v>
+        <v>1.454268431345795</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.870874696961643</v>
+        <v>1.883917593256008</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.182966376514777</v>
+        <v>2.196032630815253</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.641708903659193</v>
+        <v>2.654889912954431</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.175947112714987</v>
+        <v>3.18914585166975</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.854922456787591</v>
+        <v>2.868327584440422</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.914719397020278</v>
+        <v>2.928176690730496</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.816827422090569</v>
+        <v>2.830279710810679</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.190223604796458</v>
+        <v>3.203779651148061</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.241532238660049</v>
+        <v>3.231102602961897</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1656</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3799117501616678</v>
+        <v>-0.3912444223181026</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7862924146518537</v>
+        <v>0.7992022242279049</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.152054552814306</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5652796810763689</v>
+        <v>-0.5523005386779047</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2851879927403544</v>
+        <v>0.2982987971152937</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7034028773159164</v>
+        <v>0.7164457736102818</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.162147420913207</v>
+        <v>1.175213675213683</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.419601703291121</v>
+        <v>1.432782712586359</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.841693604548432</v>
+        <v>1.854892343503195</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.836979047539835</v>
+        <v>1.850384175192666</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.934158090372016</v>
+        <v>1.947615384082233</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.847768300857538</v>
+        <v>1.861220589577648</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.212537844502002</v>
+        <v>2.226093890853605</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.341486229918388</v>
+        <v>2.331056594220236</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1753</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6394736881506518</v>
+        <v>-0.6508063603070866</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3730257165690603</v>
+        <v>0.3859355261451114</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6493387116476015</v>
+        <v>-0.6363315802299994</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9184010382528811</v>
+        <v>-0.9054218958544169</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5441012036958455</v>
+        <v>-0.5309903993209062</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2667463244362409</v>
+        <v>0.2797892207306063</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4101928695712687</v>
+        <v>0.4232591238717447</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6845953236134932</v>
+        <v>0.697776332908731</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.022910896643971</v>
+        <v>1.036109635598734</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9714166300416025</v>
+        <v>0.9848217576944336</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8237083713258428</v>
+        <v>0.8371656650360606</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7440013974676276</v>
+        <v>0.7574536861877377</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8371523769391516</v>
+        <v>0.8507084232907545</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.029828643613619</v>
+        <v>1.019399007915467</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>1849</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8438980281602184</v>
+        <v>-0.8552307003166533</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.08644290728006609</v>
+        <v>0.09935271685611724</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6870088171640134</v>
+        <v>-0.6740016857464113</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.827172125876146</v>
+        <v>-0.8141929834776818</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5543440169894183</v>
+        <v>-0.541233212614479</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2298475151015893</v>
+        <v>0.2428904113959547</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4155302391489428</v>
+        <v>0.4285964934494189</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6514295877984821</v>
+        <v>0.6646105970937199</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.077179295991513</v>
+        <v>1.090378034946276</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8219702818667827</v>
+        <v>0.8353754095196138</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6713002458131285</v>
+        <v>0.6847575395233463</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4893502501028593</v>
+        <v>0.5028025388229693</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5017619452693651</v>
+        <v>0.515317991620968</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8055665658095776</v>
+        <v>0.7951369301114255</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.099621797148643</v>
+        <v>-1.086331276054352</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4031863753648963</v>
+        <v>-0.4174949264364969</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9230161040021798</v>
+        <v>-0.9371777679881106</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.019373700056725</v>
+        <v>-1.033462164866329</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.9212533946580379</v>
+        <v>-0.935547054916384</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3931271097230891</v>
+        <v>-0.4076197541472482</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3994584479029442</v>
+        <v>-0.4139815645648</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.02518921084828207</v>
+        <v>-0.04003938339834434</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3489952972135484</v>
+        <v>0.3339272411103522</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3418296432874399</v>
+        <v>0.3265246037061473</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2677006076173782</v>
+        <v>0.2523666065701065</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.07606241068336317</v>
+        <v>0.06082387844094228</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1434773976728962</v>
+        <v>0.1280794424203364</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2691210519631468</v>
+        <v>0.2807803130169688</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.263542388327288</v>
+        <v>-1.251815909624099</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.147132141408974</v>
+        <v>-1.159273362954849</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.801017003407189</v>
+        <v>-1.812950176597418</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.882654508584451</v>
+        <v>-1.89452715264364</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.827480001856344</v>
+        <v>-1.839513948177938</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.457453631366675</v>
+        <v>-1.46960180291741</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.766200278786087</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.389386738732135</v>
+        <v>-1.401714807786909</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.187436417335206</v>
+        <v>-1.199883661944483</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.299302178434665</v>
+        <v>-1.311905762459595</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.382965033744</v>
+        <v>-1.395586332557464</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.845540774514426</v>
+        <v>-1.857943275891394</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.811752341518201</v>
+        <v>-1.824279282046383</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.678712341270398</v>
+        <v>-1.667608123531885</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.164828931370288</v>
+        <v>-1.154616056554104</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.114316319527802</v>
+        <v>-1.124874488522892</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.485696242607702</v>
+        <v>-1.49617789470679</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.509317085877292</v>
+        <v>-1.519768932140742</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.403168509280746</v>
+        <v>-1.413784924512441</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.037593025087965</v>
+        <v>-1.048318102954838</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.409372473372926</v>
+        <v>-1.419957336706013</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.008814438112481</v>
+        <v>-1.019680369075893</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.734634897867025</v>
+        <v>-0.7456426844071018</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8935689362124748</v>
+        <v>-0.9046882885754499</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9403240042864667</v>
+        <v>-0.9514723478780809</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.326351136975838</v>
+        <v>-1.337328415872172</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.410489243912814</v>
+        <v>-1.421523221818354</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.447959989807678</v>
+        <v>-1.438339132374757</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.430495427337945</v>
+        <v>-1.421437659033074</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.436121190888997</v>
+        <v>-1.445165900171752</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.017611136224723</v>
+        <v>-2.026489855309016</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.324552381954639</v>
+        <v>-2.333285828260898</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.465459995721922</v>
+        <v>-2.474236749246195</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.020798931554076</v>
+        <v>-2.029714201377864</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.376075980271004</v>
+        <v>-2.3848640553446</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.068878415623772</v>
+        <v>-2.077884470885557</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.814908144765113</v>
+        <v>-1.824037422383086</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.0569125701102</v>
+        <v>-2.066099134804368</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.113479734360105</v>
+        <v>-2.122685588165254</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.684555152156321</v>
+        <v>-2.69352206142139</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.831010239018028</v>
+        <v>-2.839997435342589</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.935927103090982</v>
+        <v>-2.926867264685384</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.530009299368452</v>
+        <v>-1.522066589850688</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.902022161341037</v>
+        <v>-1.909640464140843</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.276346598054964</v>
+        <v>-2.283883736520025</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.716084200076708</v>
+        <v>-2.723433095185953</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.037233440628562</v>
+        <v>-3.044544217073152</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.758754932667983</v>
+        <v>-2.766134191494466</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.138383465922978</v>
+        <v>-3.145631221486909</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.190915067766042</v>
+        <v>-3.198219517214518</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.073622406085299</v>
+        <v>-3.080987508368978</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.192828135161896</v>
+        <v>-3.20028329186276</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.258268067913498</v>
+        <v>-3.265734268373834</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.676878538440036</v>
+        <v>-3.684179167446068</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.036853757602898</v>
+        <v>-4.04408263225924</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.201113682246735</v>
+        <v>-4.192662811716197</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.246694740009005</v>
+        <v>-1.239890039985454</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.61059644546016</v>
+        <v>-1.617223076333573</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.874182315748484</v>
+        <v>-1.880767774920599</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.320447179294476</v>
+        <v>-2.326853206478084</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.764925352872837</v>
+        <v>-2.771241941705561</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.597183965727886</v>
+        <v>-2.603527361948913</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.84901450403008</v>
+        <v>-2.85527946747672</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.811777631916897</v>
+        <v>-2.818123197134405</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.890563727032138</v>
+        <v>-2.896892211980251</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.011662414651653</v>
+        <v>-3.018063926251202</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.19659430207826</v>
+        <v>-3.202958445259014</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.478697763569144</v>
+        <v>-3.484956091724335</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.767077488018643</v>
+        <v>-3.773288704844063</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.058531475016224</v>
+        <v>-4.051150277421826</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.255814557833737</v>
+        <v>-1.24991061767571</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.575829053796795</v>
+        <v>-1.581493919920668</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.845952826607338</v>
+        <v>-1.851571067603309</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.369627507163322</v>
+        <v>-2.375048930936131</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.570938240649092</v>
+        <v>-2.576353847064091</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.290380075345197</v>
+        <v>-2.295864171511589</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.569188836306637</v>
+        <v>-2.574587389539104</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.486167998411254</v>
+        <v>-2.491653309421537</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.563949318670808</v>
+        <v>-2.569417568183987</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.756869972138574</v>
+        <v>-2.762371503705474</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.013675539536479</v>
+        <v>-3.019113147123377</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.137877853700971</v>
+        <v>-3.143270895458159</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.361716931519069</v>
+        <v>-3.367082630576839</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.59039611191838</v>
+        <v>-3.584072962213661</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.046601173507412</v>
+        <v>-1.041602475716559</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.361827820080997</v>
+        <v>-1.366664707716623</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.469577609467791</v>
+        <v>-1.474419789066786</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.725639632458034</v>
+        <v>-1.730385738502235</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.145245487734151</v>
+        <v>-2.149905920555064</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.796316255365802</v>
+        <v>-1.801067931352151</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.930674284664669</v>
+        <v>-1.93539187472453</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.941613276627571</v>
+        <v>-1.946375932411215</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.917181006728917</v>
+        <v>-1.921960798222734</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.175572697737273</v>
+        <v>-2.180351806344241</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.328368535129101</v>
+        <v>-2.333119150214351</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.444627041491543</v>
+        <v>-2.449337950643582</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.610219695646833</v>
+        <v>-2.6149189866995</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.815363502250555</v>
+        <v>-2.810117188257891</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.063949081533458</v>
+        <v>-1.059684287164096</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.63071887404827</v>
+        <v>-1.634665567221688</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.815856210326913</v>
+        <v>-1.819778392671978</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.958051944462362</v>
+        <v>-1.961919981608318</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.383121092772647</v>
+        <v>-2.386899332651545</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.233459674651975</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.168787556829123</v>
+        <v>-2.17262173783913</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.297102136246494</v>
+        <v>-2.300936067976153</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.115633287561067</v>
+        <v>-2.119533032347192</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.497618043948791</v>
+        <v>-2.501467676659189</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.685105486562257</v>
+        <v>-2.688914074556152</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.762394380535483</v>
+        <v>-2.766177549359114</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.004164107649942</v>
+        <v>-3.007906613729688</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.188745965811705</v>
+        <v>-3.184092017650322</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6666038099244389</v>
+        <v>-0.6631503662154046</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.095183923346227</v>
+        <v>-1.098549774810948</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.135825340231655</v>
+        <v>-1.139207660687369</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.327218164815434</v>
+        <v>-1.330534693489895</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.541925144000011</v>
+        <v>-1.545214500528033</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.443325111703103</v>
+        <v>-1.446626292160289</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.296386333843792</v>
+        <v>-1.299740422153384</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.408677746727456</v>
+        <v>-1.412031294846507</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.114567184724514</v>
+        <v>-1.118017355493457</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.424634193458715</v>
+        <v>-1.42804932273981</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.550961581595729</v>
+        <v>-1.554353869386276</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.622947050031399</v>
+        <v>-1.626316773041736</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.903102717343423</v>
+        <v>-1.906417025592049</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.16054501915086</v>
+        <v>-2.156877276543405</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.7439528747527504</v>
+        <v>-0.7411025620313154</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.9579531096448193</v>
+        <v>-0.9606701918134135</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9252998807240473</v>
+        <v>-0.928049978941452</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.014712851483516</v>
+        <v>-1.017430947877536</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.33136341166734</v>
+        <v>-1.334019730691629</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.19482351007931</v>
+        <v>-1.197505012747101</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.35218880812495</v>
+        <v>-1.354830195665954</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.332235155729762</v>
+        <v>-1.33490990158765</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.23000772427433</v>
+        <v>-1.232717505078696</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.592516896312148</v>
+        <v>-1.595168689400687</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.722224177552313</v>
+        <v>-1.724850662768553</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.789741852620303</v>
+        <v>-1.792348035526878</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.016885139491386</v>
+        <v>-2.019449266771112</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.341352889679612</v>
+        <v>-2.338230799065514</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4606884613731594</v>
+        <v>-0.4584825362557652</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7020184285145277</v>
+        <v>-0.7041856922034953</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5450783798838188</v>
+        <v>-0.5473084137471744</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5973754585620199</v>
+        <v>-0.5995862178722078</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9227462914836551</v>
+        <v>-0.9248898816921454</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.7796766177118002</v>
+        <v>-0.7818487949524382</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9057477416111155</v>
+        <v>-0.9078891753966332</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.9333867011393835</v>
+        <v>-0.9355419863010042</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9224485179387116</v>
+        <v>-0.9246107620868642</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.191112883473622</v>
+        <v>-1.193237618890485</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.210452126225995</v>
+        <v>-1.212581571878893</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.160473401004637</v>
+        <v>-1.162616680160454</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.395151936669727</v>
+        <v>-1.39724843118843</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.639828699657528</v>
+        <v>-1.63744664235788</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07889681179976549</v>
+        <v>-0.07732320283562899</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2379834392800646</v>
+        <v>-0.2396875820897719</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1024865029630035</v>
+        <v>-0.1042412152731629</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.09684004646144473</v>
+        <v>0.09503458854675984</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2095153164777486</v>
+        <v>-0.2112561367038879</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.02128672267929232</v>
+        <v>0.01949205962896627</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1301231104877658</v>
+        <v>-0.1318803327945375</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1203928867111514</v>
+        <v>-0.1221689782348889</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08486147027956292</v>
+        <v>-0.08665013614037065</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3216772557109522</v>
+        <v>-0.3234303585410103</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2392292819556019</v>
+        <v>-0.2410124486789371</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2440191387559807</v>
+        <v>-0.245800799981474</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.404066890691638</v>
+        <v>-0.4058197441656191</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6563166428534046</v>
+        <v>-0.6547044265577</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2110299316844575</v>
+        <v>0.2120524141121649</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.07690129212633678</v>
+        <v>0.0756532984033953</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4282239353925732</v>
+        <v>0.4268745313749491</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5728411120835446</v>
+        <v>0.5714562103985372</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3103661352063085</v>
+        <v>0.3090369775369339</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4652697199280951</v>
+        <v>0.463906161473723</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4996346356064763</v>
+        <v>0.4982595044706883</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4919263612064952</v>
+        <v>0.490541955620337</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.6811633041055671</v>
+        <v>0.6797273082197961</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.5528570523125538</v>
+        <v>0.5514346057249782</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6773220947814735</v>
+        <v>0.6758617026899927</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.7266307564222032</v>
+        <v>0.7251575408470146</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.6096449921077607</v>
+        <v>0.6081921499001837</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4548760041800151</v>
+        <v>0.4557518918313761</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.213688348135527</v>
+        <v>0.2142622402619878</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.07634826833709951</v>
+        <v>0.07561381697094305</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2998170170696994</v>
+        <v>0.2990206981959034</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.4438805573528057</v>
+        <v>0.4430492920756635</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3730200955109098</v>
+        <v>0.3721991789136325</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3818289189597479</v>
+        <v>0.381009340914936</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4370680732394092</v>
+        <v>0.4362330646616641</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4631067755111502</v>
+        <v>0.4622586219624907</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.6684772225804423</v>
+        <v>0.6675760621887648</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6401319469440807</v>
+        <v>0.6392262542792935</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6769120184656074</v>
+        <v>0.6759939173463039</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.7004253056884551</v>
+        <v>0.6995013145690194</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6734377936181346</v>
+        <v>0.6725146198830316</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5081358089523604</v>
+        <v>0.5085870299790471</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4093</v>
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03362341519293466</v>
+        <v>-0.0333806831382617</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04898270053111276</v>
+        <v>-0.04923802228303487</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.129748989858804</v>
+        <v>0.1294480507210807</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2001994487226142</v>
+        <v>0.1998818496600876</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1626484986323788</v>
+        <v>0.1623372466532231</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0833702942414476</v>
+        <v>0.08307970026795175</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.133927790890823</v>
+        <v>0.1336243138348721</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1192521423636919</v>
+        <v>0.1189497916484612</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1937529335954835</v>
+        <v>0.1934319661046828</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1382133665124741</v>
+        <v>0.1379015926674327</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1913242663985812</v>
+        <v>0.1909983708086997</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.166237271500421</v>
+        <v>0.1659175249641223</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.12615126251211</v>
+        <v>0.1258390732074872</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1209960800100376</v>
+        <v>0.1211830665645977</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
+++ b/workspaces/btc_daily_14days/cycle/days_to_halving.xlsx
@@ -568,781 +568,781 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 52.64</t>
+          <t>X ≈ 52.79</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.193550291594576</v>
+        <v>7.04098921043088</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.997492698631739</v>
+        <v>6.878495576020605</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.605424904749498</v>
+        <v>6.487424219716658</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.429957630165539</v>
+        <v>6.618831536982448</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.35891641494135</v>
+        <v>9.67024598870784</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.272395358321504</v>
+        <v>8.529516194900516</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.96323741334275</v>
+        <v>11.30319380656628</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.8867289519949</v>
+        <v>12.96544774470048</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.44193518056456</v>
+        <v>11.51512726179605</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.28956342285053</v>
+        <v>10.69506311663845</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>14.55743235922945</v>
+        <v>14.03717138730509</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.59544292024463</v>
+        <v>14.09882559243379</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.17906760116425</v>
+        <v>13.70730982164662</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.10279572465503</v>
+        <v>14.66900252204707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 100.2</t>
+          <t>X ≈ 100.4</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>144</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.347180273212125</v>
+        <v>2.341888052533925</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.919082986351469</v>
+        <v>4.9179507783346</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.1417873832658</v>
+        <v>3.141667008227685</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1903482313644318</v>
+        <v>-0.1908379179711659</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7277947884534939</v>
+        <v>-0.6793675309468412</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.648096082569616</v>
+        <v>1.672015415725966</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.416280768959794</v>
+        <v>6.464237736970745</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.80520225146105</v>
+        <v>10.85442073922319</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.05377960495311</v>
+        <v>10.12697603348568</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.20756250259106</v>
+        <v>9.306829395636285</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.005423088926676</v>
+        <v>9.105270370019056</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.5126497498168</v>
+        <v>12.63629799706906</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.87306134268191</v>
+        <v>15.02172148848617</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.32501794687725</v>
+        <v>12.49701670644391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 147.8</t>
+          <t>X ≈ 148</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6827486642669882</v>
+        <v>0.6774447261975425</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.928174274099142</v>
+        <v>1.927020936201608</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.777881578019247</v>
+        <v>5.777789717819054</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.20271366689974</v>
+        <v>5.202268326473877</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.666799984847437</v>
+        <v>4.715257479563782</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.380339711224224</v>
+        <v>6.404287932928426</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.589460235250321</v>
+        <v>5.637411171338904</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.8326519697832</v>
+        <v>5.88184800525142</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.43971526990434</v>
+        <v>11.51291582426747</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.177269534965717</v>
+        <v>9.276532418327591</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.683960812019279</v>
+        <v>9.783806769532433</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>11.13875845509414</v>
+        <v>11.26240229068294</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.72199153851521</v>
+        <v>10.87064694927246</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 195.4</t>
+          <t>X ≈ 195.6</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>144</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.189214626028054</v>
+        <v>-3.194558936560256</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.004118093375801</v>
+        <v>-2.005308283514061</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.013903911285766</v>
+        <v>-1.014051907647499</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.271395673041255</v>
+        <v>3.270941056600115</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7282452424894785</v>
+        <v>-0.6798344782204992</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.261228056599748</v>
+        <v>0.2851361332163407</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.209459857056281</v>
+        <v>-1.161552794878396</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.676124900378404</v>
+        <v>-1.626970029356066</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.124287709810773</v>
+        <v>-3.051151811237048</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.973555390433226</v>
+        <v>-3.874343064481991</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.87288888336446</v>
+        <v>-4.773084351993361</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.22779724525688</v>
+        <v>-6.104186700452352</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.872230582613525</v>
+        <v>-3.723590022431864</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-3.475205515778157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 243</t>
+          <t>X ≈ 243.1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>141</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-9.208372061591788</v>
+        <v>-9.213794153542977</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.966606281919042</v>
+        <v>-7.967866409796329</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.949022874432387</v>
+        <v>-6.949233040408799</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-10.35646897146195</v>
+        <v>-10.35704762046708</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.359527183199994</v>
+        <v>-7.311184844641183</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.942375897153774</v>
+        <v>-4.918511158086446</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.151599100528102</v>
+        <v>-7.10374078595153</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.204057598901421</v>
+        <v>-6.154936785990174</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.142058190624127</v>
+        <v>-4.068938073302142</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.699953505790234</v>
+        <v>-5.600760041143594</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.197393068383938</v>
+        <v>-5.097599023878061</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.455562486632566</v>
+        <v>-4.331956528737024</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.167591703972164</v>
+        <v>-4.018955735639736</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.77959198220077</v>
+        <v>-6.607593222634108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 290.6</t>
+          <t>X ≈ 290.7</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>144</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.346913352555838</v>
+        <v>2.3416306040289</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6186076606348365</v>
+        <v>-0.6197900711131581</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.75543852401475</v>
+        <v>1.755317252792452</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5019796541544963</v>
+        <v>0.501498414431012</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.812678172376195</v>
+        <v>4.861111738883537</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.417741641932359</v>
+        <v>4.441673506592409</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.641802751621782</v>
+        <v>3.689722664346995</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.675596867387796</v>
+        <v>-1.626461493796135</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.123736924844494</v>
+        <v>-3.050624811754538</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.972864157991864</v>
+        <v>-3.873678650191216</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.178506095990855</v>
+        <v>-4.078719958366136</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-7.61537660853071</v>
+        <v>-7.491785791412809</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.343249192648095</v>
+        <v>-7.194621501076703</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-7.119426497567197</v>
+        <v>-6.947427738000535</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 338.2</t>
+          <t>X ≈ 338.3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.260371411191493</v>
+        <v>-4.574716439932402</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.017584620130208</v>
+        <v>-3.386752380680115</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-10.48016522816035</v>
+        <v>-10.70124932328073</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.817986239037332</v>
+        <v>-7.11308810608876</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-11.6007637650478</v>
+        <v>-11.75873158173457</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.60074559318514</v>
+        <v>-10.79798638617515</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-10.68835124208957</v>
+        <v>-10.86166239499268</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-10.44982343828011</v>
+        <v>-10.63669161524822</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.097831774776523</v>
+        <v>-9.290285274808724</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.115594419516547</v>
+        <v>-7.341072161004803</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.739403577324815</v>
+        <v>-8.241086883061151</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-10.12520010514729</v>
+        <v>-9.573409213383023</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-9.839311792458595</v>
+        <v>-8.582891386621171</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-6.77959198220077</v>
+        <v>-5.558538849111649</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 385.8</t>
+          <t>X ≈ 385.9</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7.186176846063752</v>
+        <v>7.740075807132634</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>12.52311054424602</v>
+        <v>13.22856161204675</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.05839084578133</v>
+        <v>10.72089024053794</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.57621534395066</v>
+        <v>12.26804581910615</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.50474589440444</v>
+        <v>15.3193183193875</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>16.19078244780113</v>
+        <v>17.01060134114947</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16.80475380818851</v>
+        <v>17.66354699911935</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>17.73051738338554</v>
+        <v>18.62030812652603</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>20.44855183276242</v>
+        <v>21.4215940653902</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>26.54233592801086</v>
+        <v>27.68930766360523</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>24.95937330562693</v>
+        <v>25.36920071228177</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>27.0842194165097</v>
+        <v>27.56223667321257</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>28.06184017111501</v>
+        <v>27.88553471731185</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>29.68612905798836</v>
+        <v>29.56261954332334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 433.4</t>
+          <t>X ≈ 433.5</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>144</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.185679595812161</v>
+        <v>-3.191033934975486</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7625365188343025</v>
+        <v>0.7613937731092761</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.855395555782664</v>
+        <v>-5.855617832639787</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.80325067872144</v>
+        <v>-7.803834352348495</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.189926119109543</v>
+        <v>-4.141629064822084</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.125608267832213</v>
+        <v>-1.101732842819906</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8680803019846977</v>
+        <v>0.915955345481656</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.946366622583867</v>
+        <v>5.995536259806435</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.887498345952331</v>
+        <v>5.960634222554653</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.428375392583419</v>
+        <v>6.52757628049212</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.307862694709115</v>
+        <v>8.407667699420713</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8.345663702902435</v>
+        <v>8.46926830996312</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>7.929129835709745</v>
+        <v>8.077760873055716</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.158351280210589</v>
+        <v>8.330350039777407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 481</t>
+          <t>X ≈ 481.1</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>141</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7287152479488839</v>
+        <v>-0.734027975158078</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.335963286645487</v>
+        <v>3.334875384248889</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.239869624445589</v>
+        <v>2.239767728109896</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2514371029698523</v>
+        <v>0.250956361651518</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.127184470244849</v>
+        <v>1.175523960224155</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.233925264967588</v>
+        <v>-4.210096606030469</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.905078093357062</v>
+        <v>-2.857255848288155</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.080004026872061</v>
+        <v>-4.030928363603479</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.850291942943265</v>
+        <v>-4.777245656828917</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-8.53267151250671</v>
+        <v>-8.433573228340066</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.44811181240226</v>
+        <v>-9.348395093400242</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-12.25135160877954</v>
+        <v>-12.12781706849361</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-12.67521912449895</v>
+        <v>-12.52662450384364</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-13.16257070560502</v>
+        <v>-12.99057194603852</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 528.5</t>
+          <t>X ≈ 528.6</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>144</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.946761061735749</v>
+        <v>-5.952188228119844</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-10.29811547309945</v>
+        <v>-10.29946333044709</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-11.38399007431321</v>
+        <v>-11.38433764125256</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-11.25752848174937</v>
+        <v>-11.25820402191269</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-11.80021996387475</v>
+        <v>-11.75210002927887</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-11.50889207909503</v>
+        <v>-11.48518208927941</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.520416367530878</v>
+        <v>-9.472696852085072</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.37586107163231</v>
+        <v>-11.32688253096896</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12.13429850121098</v>
+        <v>-12.06134107319517</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.826602043912246</v>
+        <v>-8.727538563486263</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-8.340332878591056</v>
+        <v>-8.240636016629317</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-8.30858490849203</v>
+        <v>-8.185058742277462</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-8.037140676490196</v>
+        <v>-7.888550646840343</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-7.119426497567197</v>
+        <v>-6.947427738000535</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 576.1</t>
+          <t>X ≈ 576.2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.053641036987457</v>
+        <v>-5.007254957639454</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.639164093614951</v>
+        <v>-6.588629772273428</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-9.084445935749869</v>
+        <v>-8.991453792717451</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.904021131358604</v>
+        <v>-6.852774794839831</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-14.63518236805935</v>
+        <v>-14.38999955690469</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.152841988812824</v>
+        <v>-7.077192138398772</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-12.38072909928598</v>
+        <v>-12.17730523551099</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-11.82345231850402</v>
+        <v>-11.63945239064913</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-12.9181636709768</v>
+        <v>-12.68935166606166</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-13.77149543962306</v>
+        <v>-13.51654013172369</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-18.0998117374908</v>
+        <v>-16.75210503972313</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-18.0723443904492</v>
+        <v>-16.70027856903757</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-22.62137662675993</v>
+        <v>-21.14044799293032</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-21.37343566137018</v>
+        <v>-19.88934692991972</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 623.7</t>
+          <t>X ≈ 623.8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.56005216190858</v>
+        <v>-4.609553084003821</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.108886114946728</v>
+        <v>-5.13220666106848</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.353323468099347</v>
+        <v>-1.287327932464557</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8508297414198793</v>
+        <v>0.9606920680221407</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7239981145842904</v>
+        <v>-0.5874687122362303</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4301123140875163</v>
+        <v>-0.3179328815064721</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5235699332487371</v>
+        <v>0.6818472865551399</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.05754707282258664</v>
+        <v>0.2171328177135976</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.07528491053219</v>
+        <v>2.303128155277669</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.89154953809475</v>
+        <v>-1.703988913240806</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.096357076726953</v>
+        <v>-2.97065024734011</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.144145732013868</v>
+        <v>-5.03930746445107</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.60690835453358</v>
+        <v>-6.499574216016804</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.29998205312252</v>
+        <v>-4.12532371908825</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 671.3</t>
+          <t>X ≈ 671.4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-5.105984333016437</v>
+        <v>-4.472866796531754</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-8.986423216681352</v>
+        <v>-8.143644968214659</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.426261437809373</v>
+        <v>-4.935702303478912</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.803076936193023</v>
+        <v>-4.356969950266823</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.554804771827627</v>
+        <v>-8.481403241824417</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-11.16224065713694</v>
+        <v>-10.95497616781341</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-14.32872268566026</v>
+        <v>-14.63273904389656</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-11.64701901652263</v>
+        <v>-12.2320160302815</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-12.10081143507551</v>
+        <v>-13.4386918749769</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.038760186400445</v>
+        <v>-10.60232353012128</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.864648021189637</v>
+        <v>-9.552339610730044</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.227565134770046</v>
+        <v>-10.66967449981611</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.260020884081044</v>
+        <v>-10.61566877959508</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.210696338837245</v>
+        <v>-13.16355239924697</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 718.9</t>
+          <t>X ≈ 719</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>141</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.568600779600295</v>
+        <v>-3.573941612120869</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-11.53891063423632</v>
+        <v>-11.54009742068097</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-14.06134159345961</v>
+        <v>-14.06149498346393</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-13.9311164498714</v>
+        <v>-13.93161094224941</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-14.46940600296694</v>
+        <v>-14.42086008320117</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-16.29969154779977</v>
+        <v>-16.27573413885016</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-20.63972105600211</v>
+        <v>-20.59170937701179</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-20.39756984163314</v>
+        <v>-20.34832227923943</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-22.58621157262384</v>
+        <v>-22.51295446284414</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-24.14535022710989</v>
+        <v>-24.04600290181532</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-24.35005138536976</v>
+        <v>-24.25014334935109</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-28.57099238195077</v>
+        <v>-28.44729576092253</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-28.99114323526402</v>
+        <v>-28.84245368748619</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-28.76540758503765</v>
+        <v>-28.59340882547098</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>144</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2730067854112121</v>
+        <v>0.2676659528906384</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6198799013759597</v>
+        <v>-0.6210666878206155</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.152015380535829</v>
+        <v>3.151861990531508</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.976684968568634</v>
+        <v>3.976190476190631</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.827284304361825</v>
+        <v>4.875830224127597</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.124658333996756</v>
+        <v>5.148615742946369</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.572879330943849</v>
+        <v>4.622126893337565</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.900786063310122</v>
+        <v>5.974043173089818</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.050867266980106</v>
+        <v>5.150214592274679</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.5406105531642</v>
+        <v>5.640518589182875</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.269433149963966</v>
+        <v>6.393129770992211</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.460393407761664</v>
+        <v>4.609082955539492</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>141</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.696260354068535</v>
+        <v>-5.701601186589109</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.574371627144203</v>
+        <v>-6.575558413588858</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.51524230267946</v>
+        <v>-10.51539569268378</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-15.34955616618346</v>
+        <v>-15.35005065856146</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-19.43394501005913</v>
+        <v>-19.38539909029336</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-17.718131264112</v>
+        <v>-17.69417385516238</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-17.80284162337816</v>
+        <v>-17.75482994438784</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-18.97913012532092</v>
+        <v>-18.9298825629272</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-19.04011228184402</v>
+        <v>-18.96685517206433</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-20.59925093632975</v>
+        <v>-20.49990361103518</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-20.80395209458978</v>
+        <v>-20.70404405857111</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-24.31567323301444</v>
+        <v>-24.1919766119862</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-25.44504394448404</v>
+        <v>-25.29635439670621</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-26.6377480105694</v>
+        <v>-26.46574925100274</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>144</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.199215436810853</v>
+        <v>-3.204556269331427</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.647657679153816</v>
+        <v>-9.648844465598472</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.570206841686712</v>
+        <v>-6.570360231691033</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.217759475875965</v>
+        <v>-9.218253968253968</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-12.53382680674945</v>
+        <v>-12.48528088698367</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-15.01423055489214</v>
+        <v>-14.99027314594252</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-15.79338535860282</v>
+        <v>-15.7453736796125</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-21.81600955794504</v>
+        <v>-21.76676199555133</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-23.96032504780099</v>
+        <v>-23.8870679380213</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-22.03246606635307</v>
+        <v>-21.9331187410585</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-22.23716722461342</v>
+        <v>-22.13725918859475</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-20.11945573892469</v>
+        <v>-19.99575911789645</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-24.01182881446056</v>
+        <v>-23.86313926668273</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-25.17498205312307</v>
+        <v>-25.00298329355641</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>144</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.74522900763359</v>
+        <v>3.739888175113016</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.546786765290705</v>
+        <v>3.545599978846049</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.235348713869001</v>
+        <v>5.23519532386468</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.67112941301292</v>
+        <v>4.670634920634917</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.04950652658389</v>
+        <v>2.098052446349662</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2635472228855633</v>
+        <v>0.2875046318351764</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.262170196952809</v>
+        <v>2.31018187594313</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.878434886499406</v>
+        <v>3.927682448893123</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3452305077544864</v>
+        <v>0.4184876175341827</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.098278335724459</v>
+        <v>-1.998370299705783</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.01943314996404411</v>
+        <v>0.1431297709922887</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9881711855397626</v>
+        <v>1.13686073331759</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.563870942011484</v>
+        <v>-1.391872182444821</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.440941205132368</v>
+        <v>-1.446282037652942</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9006127618960562</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.295384146651095</v>
+        <v>-1.295537536655416</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.292818577530817</v>
+        <v>-3.29331306990882</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.133430876465688</v>
+        <v>1.18197679623146</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.558464480568944</v>
+        <v>3.582421889518557</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.76453426314675</v>
+        <v>2.812545942137071</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.715905335671977</v>
+        <v>3.765152898065693</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.654923179149122</v>
+        <v>3.728180288928819</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.095784524663316</v>
+        <v>2.195131849957889</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.472643650090987</v>
+        <v>0.5725516861096622</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.343901235070504</v>
+        <v>3.467597856098749</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.342190098069153</v>
+        <v>4.490879645846981</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.277145606451711</v>
+        <v>5.449144366018373</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>144</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.050784563189147</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.852342320846262</v>
+        <v>2.851155534401606</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.929793158313444</v>
+        <v>5.929639768309123</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.92112941301293</v>
+        <v>10.92063492063492</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.216173193250562</v>
+        <v>6.264719113016334</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10.59550353028615</v>
+        <v>10.64351520927647</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.739545997610513</v>
+        <v>8.78879356000423</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.76189717442107</v>
+        <v>10.83515428420076</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.217533933646777</v>
+        <v>9.316881258941351</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.09616610871991</v>
+        <v>11.19607414473859</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.13054426107524</v>
+        <v>11.25424088210348</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>12.32501794687725</v>
+        <v>12.49701670644391</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>141</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.440941205132368</v>
+        <v>-1.446282037652942</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.283591485300306</v>
+        <v>-7.284778271744962</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-9.096802586367403</v>
+        <v>-9.096955976371724</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.838917868310958</v>
+        <v>-6.839412360688961</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.377207421406652</v>
+        <v>-7.32866150164088</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-11.33515254070773</v>
+        <v>-11.31119513175812</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.164543751037733</v>
+        <v>-7.116532072047413</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-9.759271969292556</v>
+        <v>-9.710024406898839</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.274154835035191</v>
+        <v>-6.200897725255494</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-9.251733205833133</v>
+        <v>-9.15238588053856</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.16565422224944</v>
+        <v>-10.06574618623077</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.422056211738003</v>
+        <v>-9.298359590709758</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-11.26064678136347</v>
+        <v>-11.11195723358564</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-11.03491113113702</v>
+        <v>-10.86291237157035</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>144</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.911895674300254</v>
+        <v>7.90655484177968</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.49123120973508</v>
+        <v>10.49004442329042</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.56868204720242</v>
+        <v>13.5685286571981</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16.63283985991723</v>
+        <v>16.681385779683</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.54132500066342</v>
+        <v>15.56528240961303</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.53994797473058</v>
+        <v>17.5879596537209</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>17.76732377538837</v>
+        <v>17.81657133778209</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>20.48411939664329</v>
+        <v>20.55737650642299</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>21.71753393364669</v>
+        <v>21.81688125894127</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>22.90172166427554</v>
+        <v>23.00162970029422</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>22.93609981663078</v>
+        <v>23.05979643765902</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>21.82150451887293</v>
+        <v>21.97019406665076</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.96390683576613</v>
+        <v>20.13590559533279</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>144</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.50477099236641</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.157897876401897</v>
+        <v>2.156711089957241</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.846459824980037</v>
+        <v>3.846306434975716</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.060018301901806</v>
+        <v>6.059523809523803</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.438395415472783</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.430213889552313</v>
+        <v>4.454171298501926</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.598940914158298</v>
+        <v>-2.550929235167978</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.4062126642771062</v>
+        <v>0.455460226670823</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.821436158912263</v>
+        <v>-3.748179049132567</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-5.365799399686523</v>
+        <v>-5.26645207439195</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.570500557946716</v>
+        <v>-5.47059252192804</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.536122405591435</v>
+        <v>-5.41242578456319</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.567384370016029</v>
+        <v>-4.418694822238201</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.424982053122598</v>
+        <v>-6.252983293555936</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>141</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.360477234583982</v>
+        <v>6.355136402063408</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.482365961508201</v>
+        <v>5.481179175063545</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.63369386753331</v>
+        <v>8.633540477528989</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.473138869277697</v>
+        <v>9.472644376899694</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.934849316182003</v>
+        <v>8.983395235947775</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.23222334581709</v>
+        <v>9.256180754766703</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.856732844706954</v>
+        <v>9.904744523697275</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.680444342764183</v>
+        <v>8.7296919051579</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.491802611773316</v>
+        <v>6.565059721553013</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.478763248067608</v>
+        <v>8.578110573362181</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.11094152243146</v>
+        <v>11.21084955845014</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.98219910741093</v>
+        <v>14.10589572843917</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.5620482540976</v>
+        <v>13.71073780187543</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>15.20622362063607</v>
+        <v>15.37822238020274</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>144</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.300784563189069</v>
+        <v>9.295443730668495</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>11.18567565417955</v>
+        <v>11.18448886773489</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.79090426942457</v>
+        <v>10.79075087942024</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>17.17112941301293</v>
+        <v>17.17063492063492</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>17.32728430436166</v>
+        <v>17.37583022412743</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>19.70799166733009</v>
+        <v>19.7319490762797</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.92883686361948</v>
+        <v>18.9768485426098</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>19.85065710872163</v>
+        <v>19.89990467111534</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>20.48411939664327</v>
+        <v>20.55737650642296</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>21.02308948920233</v>
+        <v>21.12243681449691</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>23.59616610871991</v>
+        <v>23.69607414473859</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>22.24165537218634</v>
+        <v>22.36535199321458</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>23.90483785220627</v>
+        <v>24.0535273999841</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>23.43612905798832</v>
+        <v>23.60812781755498</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>141</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.778916950896047</v>
+        <v>7.773576118375473</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.319245394132359</v>
+        <v>8.318058607687703</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>14.30745273278153</v>
+        <v>14.30729934277721</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>13.01923816005783</v>
+        <v>13.01874366767983</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.89938832327417</v>
+        <v>13.94793424303995</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.94893142626724</v>
+        <v>16.99694310525756</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>16.4818627824805</v>
+        <v>16.53111034487421</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>20.67619977489393</v>
+        <v>20.74945688467363</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.37238026934418</v>
+        <v>23.47172759463875</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>24.58611882739602</v>
+        <v>24.6860268634147</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>26.03893669606341</v>
+        <v>26.16263331709165</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>27.03722555906207</v>
+        <v>27.18591510683989</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>29.39062078375665</v>
+        <v>29.56261954332331</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>144</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2730067854113685</v>
+        <v>0.2676659528907948</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.07456454306849025</v>
+        <v>0.0733777566238345</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.097984619464334</v>
+        <v>-3.098138009468656</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.967759475875972</v>
+        <v>-2.968253968253975</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.049506526583912</v>
+        <v>2.098052446349683</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.819786110447687</v>
+        <v>-1.795828701498074</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.210052025269412</v>
+        <v>-1.162040346279092</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2882317801672585</v>
+        <v>-0.2389842177735417</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.96753393364677</v>
+        <v>3.066881258941343</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6794994420532419</v>
+        <v>0.7794074780719171</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.377060074428492</v>
+        <v>2.52574962220632</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.908351280210596</v>
+        <v>2.080350039777258</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.519369532512393</v>
+        <v>-7.3249266397018</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.727138619948562</v>
+        <v>-3.72291853967247</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.851837012002854</v>
+        <v>-4.857397268727915</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.911392890312307</v>
+        <v>-6.949735449735456</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-5.989828428809453</v>
+        <v>-5.957503109205895</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.612162428371448</v>
+        <v>-8.647680553349929</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.696872787637616</v>
+        <v>-8.708336642575389</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-10.6237954460229</v>
+        <v>-9.914910143699473</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.60448563174275</v>
+        <v>-13.65558645653997</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-15.18433143537188</v>
+        <v>-14.47941503735495</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-13.92917857903354</v>
+        <v>-13.9428147441503</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-15.35465444127675</v>
+        <v>-15.36612948826689</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-16.50473230188943</v>
+        <v>-15.76128741483072</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.89943460786728</v>
+        <v>-11.06779810837091</v>
       </c>
     </row>
   </sheetData>
@@ -2210,521 +2210,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 28.84</t>
+          <t>X &gt; 29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4103</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07049640619308661</v>
+        <v>-0.08056857901720349</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0867454155387648</v>
+        <v>-0.09571904370018558</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1517541707984265</v>
+        <v>-0.1603375449302149</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.05701377280383468</v>
+        <v>-0.09018443263519771</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1434759295564589</v>
+        <v>-0.177131297705678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.07648175320230877</v>
+        <v>-0.109972327001465</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.02274769302518109</v>
+        <v>-0.01139152227259643</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.05670441425686334</v>
+        <v>0.04714244186248351</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.05796763512568504</v>
+        <v>0.04793693052771886</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1241913839734039</v>
+        <v>0.08974872099799569</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1284176135190052</v>
+        <v>0.09409600975995858</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1277441092025882</v>
+        <v>0.09288616563305396</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1608057341507134</v>
+        <v>0.1256521563193758</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.156214528073825</v>
+        <v>0.1204020342528338</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 76.43</t>
+          <t>X &gt; 76.58</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3951</v>
+        <v>3962</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.335245260782159</v>
+        <v>-0.3340111959561654</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3449408821144573</v>
+        <v>-0.3439179991218495</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3980294901805763</v>
+        <v>-0.3969186678012875</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3298874458049994</v>
+        <v>-0.3289454754711585</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5262510491736876</v>
+        <v>-0.5275806155714875</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4172153153535234</v>
+        <v>-0.4174351946410937</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4124409983759136</v>
+        <v>-0.4140559673423283</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4109046805126439</v>
+        <v>-0.412595328884656</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3569377879427051</v>
+        <v>-0.3601584346183841</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2827470046872662</v>
+        <v>-0.2876741285187379</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3974690286936777</v>
+        <v>-0.4021113673813517</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3995524306075922</v>
+        <v>-0.4055584227513265</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3501104158998984</v>
+        <v>-0.357693055899496</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3885355838744644</v>
+        <v>-0.3973548230866299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 124</t>
+          <t>X &gt; 124.2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3807</v>
+        <v>3818</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4367081651412832</v>
+        <v>-0.4349356306818208</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5440528960517028</v>
+        <v>-0.5423750719227272</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.531923272627715</v>
+        <v>-0.5303802543251592</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3351655248382102</v>
+        <v>-0.3341543513957319</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5186276453238676</v>
+        <v>-0.5218558078674462</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.4953358410432855</v>
+        <v>-0.4962410846077887</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6707378028141378</v>
+        <v>-0.67347825477583</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.83515458810502</v>
+        <v>-0.8375430276294296</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.7507237886196165</v>
+        <v>-0.7556920552069073</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6417185226930684</v>
+        <v>-0.6495412074811213</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7531339787691493</v>
+        <v>-0.7606925539150495</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.8879572412146644</v>
+        <v>-0.8974461452379998</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.9259277873828964</v>
+        <v>-0.93774431163326</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.8836799933989425</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 171.6</t>
+          <t>X &gt; 171.8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4797641970415967</v>
+        <v>-0.4775914996837258</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6391385564421199</v>
+        <v>-0.6370677118861536</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.7746080745756814</v>
+        <v>-0.7722763560581924</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5481608783665948</v>
+        <v>-0.5464566624045943</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7180671695612304</v>
+        <v>-0.7226806578885956</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7597849007458777</v>
+        <v>-0.7608520695065124</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9115146504320109</v>
+        <v>-0.9154786379909936</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.091608686485344</v>
+        <v>-1.095208008765191</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.219586829332066</v>
+        <v>-1.226149958662411</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.0193719095261</v>
+        <v>-1.03017117246317</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.154560701491775</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.35052322953424</v>
+        <v>-1.363733507072332</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.373924684532817</v>
+        <v>-1.390554528600283</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.296776924917623</v>
+        <v>-1.316894090401341</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 219.2</t>
+          <t>X &gt; 219.3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3522</v>
+        <v>3533</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3689859852942803</v>
+        <v>-0.3668518136066723</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5833301937736195</v>
+        <v>-0.5813001935407272</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7648242584239853</v>
+        <v>-0.7624219322175847</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7043267339607766</v>
+        <v>-0.7020483045038546</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7176510302932897</v>
+        <v>-0.7244270065645679</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.8015298938911855</v>
+        <v>-0.8034850446528665</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8993329043349334</v>
+        <v>-0.9054490091792857</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.067710238217146</v>
+        <v>-1.073534153411359</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.141711495206877</v>
+        <v>-1.151765507269616</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8985875764055393</v>
+        <v>-0.9142468156981849</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.002533654873474</v>
+        <v>-1.017978142843113</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.151111685450175</v>
+        <v>-1.170519451072693</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.271779298580626</v>
+        <v>-1.295463356476944</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.200677680607136</v>
+        <v>-1.228924420077462</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 266.8</t>
+          <t>X &gt; 266.9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3381</v>
+        <v>3392</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.0003514284300578652</v>
+        <v>0.0009013909720394508</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2754207207098816</v>
+        <v>-0.2742524823107573</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5069206781645406</v>
+        <v>-0.505246116694309</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3017972883862043</v>
+        <v>-0.3007054673721328</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4406606317248674</v>
+        <v>-0.450626046903956</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6288415512529042</v>
+        <v>-0.6324300086876136</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6385906583535004</v>
+        <v>-0.6477959606754808</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8535058673634026</v>
+        <v>-0.862308395394372</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.016586122815916</v>
+        <v>-1.030503322183947</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6983531498917159</v>
+        <v>-0.7194359770225347</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8275927565283183</v>
+        <v>-0.8483948456066912</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.013304065525091</v>
+        <v>-1.039103581983468</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.15101338637708</v>
+        <v>-1.182252146140286</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.9680166582691569</v>
+        <v>-1.00534178412213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 314.4</t>
+          <t>X &gt; 314.5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3237</v>
+        <v>3248</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1047709923664044</v>
+        <v>-0.1028747810353963</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2601538318160976</v>
+        <v>-0.2589330818219793</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6075631635256258</v>
+        <v>-0.6054681380015978</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3375538159505638</v>
+        <v>-0.3362711567131527</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6743587434920997</v>
+        <v>-0.6861218108058651</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8533420084103653</v>
+        <v>-0.8573902630596351</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8290066765915114</v>
+        <v>-0.8400997420804259</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8169346273252458</v>
+        <v>-0.8284296865982412</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9228481816691385</v>
+        <v>-0.940941285700525</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5526844488826228</v>
+        <v>-0.579592705798305</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.6785252493047764</v>
+        <v>-0.7051784612971588</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7196066771430125</v>
+        <v>-0.753024075161477</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8755478454122851</v>
+        <v>-0.9156938988770875</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6943672863634092</v>
+        <v>-0.7418995497137288</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 362</t>
+          <t>X &gt; 362.1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3096</v>
+        <v>3104</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.08448600345217727</v>
+        <v>0.104581790769096</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1345731660692238</v>
+        <v>-0.1138280628027886</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1579388446905199</v>
+        <v>-0.137107155179379</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.04241784319371078</v>
+        <v>-0.02188274153593284</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1767414605336555</v>
+        <v>-0.1724440379277326</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4094195583285654</v>
+        <v>-0.3962285872449982</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3799861392093291</v>
+        <v>-0.3751818870484058</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.378227481865089</v>
+        <v>-0.3734072259907606</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5505378823706408</v>
+        <v>-0.553600585174884</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2537922312277772</v>
+        <v>-0.2659158238557353</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3114116045209201</v>
+        <v>-0.3555744623493453</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2912511624955272</v>
+        <v>-0.3438309501924337</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4673144098394388</v>
+        <v>-0.5599991700642164</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4172301151382598</v>
+        <v>-0.5184472110818632</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 409.6</t>
+          <t>X &gt; 409.7</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2952</v>
+        <v>2963</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2619379400898509</v>
+        <v>-0.2587677388654797</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.7520211519382585</v>
+        <v>-0.7487510949167913</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6562963905671921</v>
+        <v>-0.6538056475169185</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6091804376885577</v>
+        <v>-0.6067224064196779</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8929115754086823</v>
+        <v>-0.9096490640436414</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.219185509847087</v>
+        <v>-1.224565752247912</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.218266136643372</v>
+        <v>-1.233589167827908</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.261580889926101</v>
+        <v>-1.277259357177009</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.574883722133237</v>
+        <v>-1.59933208896485</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.560920434117477</v>
+        <v>-1.596218392783179</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.544132819650081</v>
+        <v>-1.57973689894164</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.626639971227483</v>
+        <v>-1.671794343678805</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.858980486959176</v>
+        <v>-1.913634093493187</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.885686660168822</v>
+        <v>-1.949912081946238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 457.2</t>
+          <t>X &gt; 457.3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2808</v>
+        <v>2819</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1120024705656277</v>
+        <v>-0.1089818813841603</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.8296907760804473</v>
+        <v>-0.8258922304243299</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3896759205561366</v>
+        <v>-0.3880869690289117</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2402537586612326</v>
+        <v>-0.2390799373832238</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7238339065009498</v>
+        <v>-0.7445532427906798</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.223984342770926</v>
+        <v>-1.230840296042736</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.325258261701222</v>
+        <v>-1.343392080178596</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.63121922390097</v>
+        <v>-1.648767895256341</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.957569982035061</v>
+        <v>-1.98550986436706</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.970627912409817</v>
+        <v>-2.011197616958995</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.049363358847984</v>
+        <v>-2.089912940858703</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.138040159644412</v>
+        <v>-2.189819537763391</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.360934862480647</v>
+        <v>-2.424013971174297</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.400765528906227</v>
+        <v>-2.475047855457483</v>
       </c>
     </row>
     <row r="16">
@@ -2734,309 +2734,309 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2667</v>
+        <v>2678</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.07939785803805677</v>
+        <v>-0.07607243432585875</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.049922205718374</v>
+        <v>-1.044961772496364</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5286957637677077</v>
+        <v>-0.5264467570410716</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2662486636068522</v>
+        <v>-0.2648809523809561</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8216942706258692</v>
+        <v>-0.8456476735692817</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.064853607851639</v>
+        <v>-1.073978780094912</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.24173572841908</v>
+        <v>-1.263685287309499</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.501755910358057</v>
+        <v>-1.523344211149933</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.80463642504666</v>
+        <v>-1.838521534741538</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.623703222640927</v>
+        <v>-1.673051626964693</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.658203429357485</v>
+        <v>-1.70774491116925</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.603365651084964</v>
+        <v>-1.666571721544955</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.815635244578672</v>
+        <v>-1.892099077557276</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.831806200104381</v>
+        <v>-1.921392554198363</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 552.3</t>
+          <t>X &gt; 552.4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2523</v>
+        <v>2534</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2554813735641943</v>
+        <v>0.2578504837113655</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5220823997322981</v>
+        <v>-0.5190548173484189</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.09086919093643786</v>
+        <v>0.0905762450609231</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3610776518162666</v>
+        <v>0.3598382749326063</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1950958957436484</v>
+        <v>-0.2258650614058269</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4687610435000522</v>
+        <v>-0.4823397601570534</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7692307692307665</v>
+        <v>-0.7971905496111162</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9381922388465753</v>
+        <v>-0.9662370611681155</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.215071883244185</v>
+        <v>-1.257587827741808</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.212598414768131</v>
+        <v>-1.272165234360472</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.276821486951768</v>
+        <v>-1.336499323487224</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.220665859936865</v>
+        <v>-1.296144676957155</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.460543376883365</v>
+        <v>-1.551337820265744</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.530015743174275</v>
+        <v>-1.635777295134623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 599.9</t>
+          <t>X &gt; 600</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2426</v>
+        <v>2435</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4677587329308466</v>
+        <v>0.4719143189038633</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.277499990702367</v>
+        <v>-0.2722835974151252</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4577305129844831</v>
+        <v>0.4598251049131008</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6515618158591181</v>
+        <v>0.6530820917323936</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3822694743365744</v>
+        <v>0.3500073472407337</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2015080131227549</v>
+        <v>-0.2142122918014309</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3049622869490918</v>
+        <v>-0.3345082687470153</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5029613123310028</v>
+        <v>-0.5322952469510156</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7471411728525652</v>
+        <v>-0.7928056429394843</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7104496054478844</v>
+        <v>-0.7743446533177831</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6041792551701235</v>
+        <v>-0.7097457440591484</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5468765699699745</v>
+        <v>-0.6698575084495673</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6144589476838505</v>
+        <v>-0.7549017187898457</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.736606125670157</v>
+        <v>-0.8936403777450082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 647.5</t>
+          <t>X &gt; 647.6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2330</v>
+        <v>2341</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6749131732332501</v>
+        <v>0.6759544452914383</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.07843858815839155</v>
+        <v>-0.07713931378273742</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5323490461106886</v>
+        <v>0.5299799043635502</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6433516352351489</v>
+        <v>0.6407303882846165</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4278495981719388</v>
+        <v>0.3876505550967053</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1920891234692661</v>
+        <v>-0.2100475180157488</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.339099236794155</v>
+        <v>-0.3753187865592338</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5260552200454924</v>
+        <v>-0.5623876169119271</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8634299728546821</v>
+        <v>-0.9171190889165928</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6617862605834546</v>
+        <v>-0.7370159218215093</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.542698967243318</v>
+        <v>-0.6189618810482926</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3986629049243859</v>
+        <v>-0.4944075742914578</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4087614613930484</v>
+        <v>-0.5242314006611224</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.630990636813749</v>
+        <v>-0.7638760744189668</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 695.1</t>
+          <t>X &gt; 695.2</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2218</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9668250400952658</v>
+        <v>0.9614842075746921</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3713784895668368</v>
+        <v>0.3701917031221811</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8332346972374012</v>
+        <v>0.8330813072330798</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9183741780665144</v>
+        <v>0.9178796856885114</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8309412525632567</v>
+        <v>0.8794871723290285</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3618590152912233</v>
+        <v>0.3858164242408364</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3673199815435382</v>
+        <v>0.4153316605338588</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.03550832603451681</v>
+        <v>0.08475588842823356</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2959878070437085</v>
+        <v>-0.2227306972640122</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2892790109479648</v>
+        <v>-0.1899316856533915</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2234661926527011</v>
+        <v>-0.1235581566340258</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.05383105201964611</v>
+        <v>0.06986556900859853</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1132966032591156</v>
+        <v>0.035392944518712</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2482462551065225</v>
+        <v>-0.07624749553986021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 742.7</t>
+          <t>X &gt; 742.8</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2077</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.27471865616512</v>
+        <v>1.269377823644547</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.17992483836619</v>
+        <v>1.178738051921535</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.844373482498973</v>
+        <v>1.844220092494652</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.926452261137889</v>
+        <v>1.925957768759886</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.86962635753666</v>
+        <v>1.918172277302432</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.492951277879492</v>
+        <v>1.516908686829105</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.793411838208897</v>
+        <v>1.841423517199217</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.42263592432105</v>
+        <v>1.471883486714766</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.217214672949936</v>
+        <v>1.290471782729632</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.330223175608999</v>
+        <v>1.429570500903573</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.414400207045482</v>
+        <v>1.514308243064157</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.882095643945824</v>
+        <v>2.005792264974069</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.847115710227982</v>
+        <v>1.995805258005809</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.687680440858948</v>
+        <v>1.85967920042561</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1933</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.349341785698776</v>
+        <v>1.344000953178202</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.314002377177815</v>
+        <v>1.312815590733159</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.74695991120187</v>
+        <v>1.746806521197549</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.773718939942846</v>
+        <v>1.773224447564843</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.649293846236709</v>
+        <v>1.697839766002481</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.222405071940081</v>
+        <v>1.246362480889694</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.655025286910849</v>
+        <v>1.70303696590117</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.18795664312411</v>
+        <v>1.237204205517827</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8683091994828587</v>
+        <v>0.941566309262555</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.053051551626879</v>
+        <v>1.152398876921453</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.107015680485155</v>
+        <v>1.20692371650383</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.555258292230036</v>
+        <v>1.678954913258281</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.652438013153557</v>
+        <v>1.801127560931384</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.671241433685317</v>
+        <v>1.84324019325198</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1792</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.903711150490729</v>
+        <v>1.898370317970155</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.934683590687527</v>
+        <v>1.933496804242871</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.711787205932488</v>
+        <v>2.711633815928167</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.121030206663711</v>
+        <v>3.120535714285708</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.308187082139447</v>
+        <v>3.356733001905219</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.712703968917396</v>
+        <v>2.736661377867009</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.186029323936935</v>
+        <v>3.234041002927256</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.774764251578766</v>
+        <v>2.824011813972483</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.434764237913143</v>
+        <v>2.508021347692839</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.756720441583283</v>
+        <v>2.856067766877857</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.831037140465938</v>
+        <v>2.930945176484613</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.590861721392692</v>
+        <v>3.714558342420936</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.784550153793575</v>
+        <v>3.933239701571402</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.898678661162954</v>
+        <v>4.070677420729616</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1648</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.349597939672421</v>
+        <v>2.344257107151847</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.946732827858128</v>
+        <v>2.945546041413472</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.522835229510854</v>
+        <v>3.522681839506532</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.19917687795359</v>
+        <v>4.198682385575587</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.692440722916146</v>
+        <v>4.740986642681918</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.261659412745409</v>
+        <v>4.285616821695022</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.844424781634586</v>
+        <v>4.892436460624907</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.923472642702208</v>
+        <v>4.972720205095925</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.741131262878461</v>
+        <v>4.814388372658158</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.922765864606859</v>
+        <v>5.022113189901432</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.021462764599093</v>
+        <v>5.121370800617768</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.662637033459262</v>
+        <v>5.786333654487507</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.213359966553632</v>
+        <v>6.36204951433146</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.439095616780165</v>
+        <v>6.611094376346827</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1504</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.215973688484652</v>
+        <v>2.210632855964079</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.889280855125222</v>
+        <v>2.888094068680566</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.358871172497842</v>
+        <v>3.358717782493521</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.153989933107482</v>
+        <v>4.153495440729479</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.945487614054343</v>
+        <v>4.994033533820115</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.644457388370284</v>
+        <v>4.668414797319898</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.091661922721137</v>
+        <v>5.139673601711458</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.023529449147162</v>
+        <v>5.072777011540879</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.162015377730761</v>
+        <v>5.235272487510457</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.37592636863495</v>
+        <v>5.475273693929523</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.703140103991771</v>
+        <v>5.803048140010446</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.202943788261997</v>
+        <v>6.326640409290242</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.713643998778373</v>
+        <v>6.862333546556201</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.205337095813412</v>
+        <v>7.377335855380075</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1363</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.59427522920366</v>
+        <v>2.588934396683086</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.281338815506736</v>
+        <v>3.28015202906208</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.840345860685666</v>
+        <v>3.840192470681345</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.924349434207997</v>
+        <v>4.923854941829994</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.339838311046272</v>
+        <v>5.388384230812044</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.756801482280771</v>
+        <v>4.780758891230384</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.332399266815038</v>
+        <v>5.380410945805359</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.158800909161833</v>
+        <v>5.20804847155555</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.317921467239202</v>
+        <v>5.391178577018898</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.715251386976838</v>
+        <v>5.814598712271412</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.24422594405047</v>
+        <v>6.344133980069145</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.498706811005938</v>
+        <v>6.622403432034183</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.958966816093124</v>
+        <v>7.107656363870952</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.404805180919801</v>
+        <v>7.576803940486464</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1219</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.540347957592573</v>
+        <v>2.535007125071999</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.332016006016261</v>
+        <v>3.330829219571605</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.593520257028239</v>
+        <v>3.593366867023917</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.215952127441867</v>
+        <v>4.215457635063864</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.236317209292849</v>
+        <v>5.284863129058621</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.385208876335653</v>
+        <v>4.409166285285266</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.710670789423865</v>
+        <v>4.758682468414186</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.7358088724624</v>
+        <v>4.785056434856116</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.674826715939624</v>
+        <v>4.74808382571932</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.301528100085562</v>
+        <v>5.400875425380136</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.671068123121515</v>
+        <v>5.77097615914019</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.951549638889475</v>
+        <v>6.075246259917719</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.35174333028484</v>
+        <v>6.500432878062668</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.823582343924002</v>
+        <v>6.995581103490665</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1078</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.061091716353438</v>
+        <v>3.055750883832864</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.720513831874918</v>
+        <v>4.719327045430262</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.253386231906518</v>
+        <v>5.253232841902197</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.661904510930874</v>
+        <v>5.661410018552871</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.886138148929803</v>
+        <v>6.934684068695574</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.441397150735568</v>
+        <v>6.465354559685181</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.263922412990745</v>
+        <v>6.311934091981065</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.631733175511982</v>
+        <v>6.680980737905699</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.10692912659588</v>
+        <v>6.180186236375576</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.205062278317975</v>
+        <v>7.304409603612548</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.742476147887103</v>
+        <v>7.842384183905779</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.962383057199737</v>
+        <v>8.086079678227982</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.655404745630307</v>
+        <v>8.804094293408134</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.159433531292841</v>
+        <v>9.331432290859503</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>934</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.313216159667853</v>
+        <v>2.307875327147279</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.830810081969275</v>
+        <v>3.82962329552462</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.971370602995812</v>
+        <v>3.97121721299149</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.636927652365763</v>
+        <v>4.63643315998776</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.383434673145871</v>
+        <v>5.431980592911643</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.038410415843053</v>
+        <v>5.062367824792666</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.525434531951625</v>
+        <v>4.573446210941945</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.914896937415413</v>
+        <v>4.96414449980913</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.890317350485788</v>
+        <v>3.963574460265484</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.967593414969642</v>
+        <v>5.066940740264215</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.40529054364734</v>
+        <v>5.505198579666015</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.6538014583153</v>
+        <v>5.777498079343545</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.625513560034008</v>
+        <v>6.774203107811836</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.493647497198452</v>
+        <v>7.665646256765115</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>790</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.191431539279158</v>
+        <v>3.186090706758584</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.135745977667639</v>
+        <v>4.134559191222984</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.994139149874627</v>
+        <v>3.993985759870306</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.377528850425016</v>
+        <v>4.377034358047013</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.737973474544511</v>
+        <v>5.786519394310282</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.149271554812508</v>
+        <v>5.173228963762121</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.824054866432419</v>
+        <v>5.87206654542274</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.736733058088717</v>
+        <v>5.785980620482434</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.296004066122904</v>
+        <v>5.369261175902601</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.851148560932288</v>
+        <v>6.950495886226861</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.405941073558161</v>
+        <v>7.505849109576836</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.693483782875511</v>
+        <v>7.817180403903755</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.665737992853252</v>
+        <v>8.81442754063108</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.03071414940889</v>
+        <v>10.20271290897555</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>649</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.502933167880116</v>
+        <v>2.497592335359542</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.84318293033094</v>
+        <v>3.841996143886284</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.986161930783915</v>
+        <v>2.986008540779594</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.270470279302941</v>
+        <v>3.269975786924938</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.043428800167185</v>
+        <v>5.091974719932956</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.262220395287628</v>
+        <v>4.286177804237241</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.947926060674781</v>
+        <v>4.995937739665102</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.097190236610686</v>
+        <v>5.146437799004403</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.03620808008791</v>
+        <v>5.109465189867606</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.497537357717988</v>
+        <v>6.596884683012561</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.601002609319124</v>
+        <v>6.7009106453378</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.327214351813119</v>
+        <v>6.450910972841363</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.601978752736997</v>
+        <v>7.750668300514825</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.906296837478159</v>
+        <v>9.078295597044821</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>505</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.5645359383266637</v>
+        <v>0.55919510580609</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.749482034817667</v>
+        <v>1.748295248373012</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7606512441220303</v>
+        <v>0.760497854117709</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6932820281311933</v>
+        <v>-0.6937765205091964</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.54070564649588</v>
+        <v>1.589251566261652</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1421183436710081</v>
+        <v>-0.118160934721395</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.9612901089440129</v>
+        <v>1.009301787934334</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.8902610691176704</v>
+        <v>0.9395086315113872</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.6312591106146996</v>
+        <v>0.704516220394396</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.355597740027406</v>
+        <v>2.454945065321979</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.754856977806817</v>
+        <v>1.854765013825492</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.78923513016214</v>
+        <v>1.912931751190385</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.953242692690317</v>
+        <v>3.101932240468145</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.763136758758435</v>
+        <v>4.935135518325097</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>364</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.23004571764114</v>
+        <v>-2.235386550161714</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7953988268948819</v>
+        <v>-0.7965856133395377</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.005000013116508</v>
+        <v>-6.005494505494511</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.246586269508896</v>
+        <v>-3.198040349743124</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.872289162950736</v>
+        <v>-4.848331754001123</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.231724796942181</v>
+        <v>-5.183713117951861</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.133401970878069</v>
+        <v>-7.060144861098372</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.785518569405738</v>
+        <v>-5.686171244111165</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.089120826567026</v>
+        <v>-6.989212790548351</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-7.60419322366225</v>
+        <v>-7.480496602634005</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.375992428624016</v>
+        <v>-6.227302880846189</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.776630404771097</v>
+        <v>-4.604631645204435</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>220</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-3.86840735600277</v>
+        <v>-3.873748188523344</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.364829396325462</v>
+        <v>-1.366016182770117</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-5.395964417444127</v>
+        <v>-5.396117807448448</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-7.993012001128498</v>
+        <v>-7.993506493506501</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.713119736042373</v>
+        <v>-6.664573816276601</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.870291160952739</v>
+        <v>-6.846333752003126</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.864092429309814</v>
+        <v>-7.816080750319493</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.331161073096553</v>
+        <v>-8.281913510702836</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.02850686598297</v>
+        <v>-11.95524975620327</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.51478929867646</v>
+        <v>-11.41544197338189</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-12.17403591148211</v>
+        <v>-12.07412787546343</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-12.59420321367224</v>
+        <v>-12.470506592644</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.10526315789474</v>
+        <v>-11.95657361011691</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.152254780395481</v>
+        <v>-8.980256020828818</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.5072772004046797</v>
+        <v>1.607535233936545</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>2.534403900498212</v>
+        <v>2.377299325251279</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.294102424015868</v>
+        <v>-6.251732780710483</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-9.77833511175281</v>
+        <v>-9.65126050420168</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.906986110631635</v>
+        <v>-7.78756846868302</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-3.995154249671252</v>
+        <v>-3.985371185158208</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-6.489503163154282</v>
+        <v>-6.398968450854255</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-4.546933252724159</v>
+        <v>-5.688330623002301</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.427192517680666</v>
+        <v>-9.254714996844982</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.457834205576795</v>
+        <v>-6.54913181295408</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-9.276993195162284</v>
+        <v>-9.106213436960765</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.037795765698526</v>
+        <v>-7.871576111360575</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.843488787686638</v>
+        <v>-5.913792861453814</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.617753137460106</v>
+        <v>-5.664747999438447</v>
       </c>
     </row>
   </sheetData>
@@ -3904,521 +3904,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 28.84</t>
+          <t>X &lt; 29</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.447609960014546</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-2.756115557069066</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.841193893825476</v>
+        <v>-7.692504346047649</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.615458243598944</v>
+        <v>-7.443459484032282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 76.43</t>
+          <t>X &lt; 76.58</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>228</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.828562340966926</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.995617174647428</v>
+        <v>5.994430388202773</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.916635263576609</v>
+        <v>6.916481873572287</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.731070933480751</v>
+        <v>5.730576441102748</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.140149801437694</v>
+        <v>9.188695721203466</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.244541374932432</v>
+        <v>7.268498783882045</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.159831015666263</v>
+        <v>7.207842694656584</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.1313588631076</v>
+        <v>7.180606425501317</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.19318372412868</v>
+        <v>6.266440833908376</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.904668436570745</v>
+        <v>5.004015761865318</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.892949734450902</v>
+        <v>6.992857770469577</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.068580542264741</v>
+        <v>6.217270090042568</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.732912683719348</v>
+        <v>6.904911443286011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 124</t>
+          <t>X &lt; 124.2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>372</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.48447631946155</v>
+        <v>4.479135486940976</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.585317231240531</v>
+        <v>5.584130444795875</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.459363050786564</v>
+        <v>5.459209660782243</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.439050559966326</v>
+        <v>3.438556067588323</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.320115845580311</v>
+        <v>5.368661765346083</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.079855466613246</v>
+        <v>5.103812875562859</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.876865537454606</v>
+        <v>6.924877216444926</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.560334528076467</v>
+        <v>8.609582090470184</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.692900758650467</v>
+        <v>7.766157868430163</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.574164758019528</v>
+        <v>6.673512083314101</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.713549621264711</v>
+        <v>7.813457657283386</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.092013795125403</v>
+        <v>9.215710416153648</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>9.478314554715226</v>
+        <v>9.627004102493053</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.897598592038527</v>
+        <v>9.069597351605189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 171.6</t>
+          <t>X &lt; 171.8</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>513</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.440648110947436</v>
+        <v>3.435307278426862</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.582361814023656</v>
+        <v>4.581175027579</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.552112846422602</v>
+        <v>5.551959456418281</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.927952025098691</v>
+        <v>3.927457532720688</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.14404843691527</v>
+        <v>5.192594356681042</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.441422466550357</v>
+        <v>5.46537987549997</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.526302750559047</v>
+        <v>6.574314429549368</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.813620071684589</v>
+        <v>7.862867634078306</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8.727296784557524</v>
+        <v>8.80055389433722</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.292582666590242</v>
+        <v>7.391929991884815</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.257472151604901</v>
+        <v>8.357380187623576</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.656372721114217</v>
+        <v>9.780069342142461</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>9.821017189438237</v>
+        <v>9.969706737216065</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.267025744148206</v>
+        <v>9.439024503714869</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 219.2</t>
+          <t>X &lt; 219.3</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>657</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.98533555253465</v>
+        <v>1.979994720014076</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.13773044870014</v>
+        <v>3.136543662255484</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.112822077643735</v>
+        <v>4.112668687639413</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.786426216665888</v>
+        <v>3.785931724287884</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.856964669658467</v>
+        <v>3.905510589424239</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.306545700815633</v>
+        <v>4.330503109765246</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.830663347637746</v>
+        <v>4.878675026628066</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.733457717549634</v>
+        <v>5.78270527994335</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.129096565593066</v>
+        <v>6.202353675372763</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.822556764696998</v>
+        <v>4.921904089991571</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>5.378890614047158</v>
+        <v>5.478798650065833</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.174303774012827</v>
+        <v>6.298000395041072</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.819601931353915</v>
+        <v>6.968291479131743</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.436509575492167</v>
+        <v>6.608508335058829</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 266.8</t>
+          <t>X &lt; 266.9</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>798</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.001494671793992097</v>
+        <v>-0.003846160726581616</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.171055771138668</v>
+        <v>1.169868984694013</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.154730501671843</v>
+        <v>2.154577111667521</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.282449379596038</v>
+        <v>1.281954887218035</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.871979375372533</v>
+        <v>1.920525295138305</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.670606537839703</v>
+        <v>2.694563946789316</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.71120946178155</v>
+        <v>2.759221140771871</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.622586933283038</v>
+        <v>3.671834495676755</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.962312546846434</v>
+        <v>3.061659872141007</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.50949108783437</v>
+        <v>3.609399123853045</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.295748939437807</v>
+        <v>4.419445560466052</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.878104351788558</v>
+        <v>5.026793899566385</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.101333736350931</v>
+        <v>4.273332495917593</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 314.4</t>
+          <t>X &lt; 314.5</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>942</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.361471045850152</v>
+        <v>0.3561302133295783</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8972821651491643</v>
+        <v>0.8960953787045085</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.094867468292215</v>
+        <v>2.094714078287893</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.163521486615181</v>
+        <v>1.163026994237178</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.323745733944115</v>
+        <v>2.372291653709887</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.939591101158818</v>
+        <v>2.963548510108431</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.85488074189265</v>
+        <v>2.902892420882971</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.812440548212074</v>
+        <v>2.86168811060579</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.176086841795453</v>
+        <v>3.249343951575149</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.901539595359438</v>
+        <v>2.000886920654011</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.333781112258478</v>
+        <v>2.433689148277153</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.47431637714034</v>
+        <v>2.598012998168585</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.009579536565788</v>
+        <v>3.158269084343615</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.386058286580003</v>
+        <v>2.558057046146665</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 362</t>
+          <t>X &lt; 362.1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2425364586637286</v>
+        <v>-0.3001670735057616</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3861988920989603</v>
+        <v>0.3266005927195934</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4531080244260934</v>
+        <v>0.3932677609426491</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1216526509322833</v>
+        <v>0.06274664561956911</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5067241320009472</v>
+        <v>0.4943078177431559</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.173442575301777</v>
+        <v>1.135417461792287</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.088732216035609</v>
+        <v>1.074761372566826</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.083344089331042</v>
+        <v>1.069333768721236</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.576378553306888</v>
+        <v>1.584847347429744</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7264597569770288</v>
+        <v>0.761018766614761</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8911030123825725</v>
+        <v>1.017283475616431</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.8331450613214599</v>
+        <v>0.9833691816737655</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.336355242172417</v>
+        <v>1.601102599492997</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.192746478733206</v>
+        <v>1.481823336278161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 409.6</t>
+          <t>X &lt; 409.7</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1227</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6329633189620338</v>
+        <v>0.6276224864414601</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.816618332799536</v>
+        <v>1.81543154635488</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.584846133048579</v>
+        <v>1.584692743044258</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.470572499130817</v>
+        <v>1.470078006752814</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.154776833565684</v>
+        <v>2.203322753331456</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.941148418213004</v>
+        <v>2.965105827162617</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.937937651448877</v>
+        <v>2.985949330439198</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.041366155176398</v>
+        <v>3.090613717570115</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.795379923673998</v>
+        <v>3.868637033453695</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.760457052364508</v>
+        <v>3.859804377659081</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.718755079108391</v>
+        <v>3.818663115127066</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.916132416467789</v>
+        <v>4.039829037496034</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.473976673178832</v>
+        <v>4.62266622095666</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.536713138401289</v>
+        <v>4.708711897967952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 457.2</t>
+          <t>X &lt; 457.3</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1371</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2304587669333742</v>
+        <v>0.2251179344128005</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.706584966117354</v>
+        <v>1.705398179672699</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8012373596263558</v>
+        <v>0.8010839696220344</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4938257417267522</v>
+        <v>0.4933312493487492</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.48726485383893</v>
+        <v>1.535810773604702</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.514033485953966</v>
+        <v>2.537990894903579</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.721080967679768</v>
+        <v>2.769092646670089</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.34810422761295</v>
+        <v>3.397351790006667</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.016516673570109</v>
+        <v>4.089773783349806</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.041871400216181</v>
+        <v>4.141218725510754</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.201867543195966</v>
+        <v>4.301775579214642</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.382124616047271</v>
+        <v>4.505821237075516</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.8372472857098</v>
+        <v>4.985936833487628</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.917104015440344</v>
+        <v>5.089102775007007</v>
       </c>
     </row>
     <row r="16">
@@ -4431,306 +4431,306 @@
         <v>1512</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1407316531362426</v>
+        <v>0.1353908206156689</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.936406914927197</v>
+        <v>0.9362535249228756</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4713939632774711</v>
+        <v>0.470899470899468</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.454268431345795</v>
+        <v>1.502814351111567</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.883917593256008</v>
+        <v>1.907875002205621</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.196032630815253</v>
+        <v>2.244044309805574</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.654889912954431</v>
+        <v>2.704137475348148</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.18914585166975</v>
+        <v>3.262402961449446</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.868327584440422</v>
+        <v>2.967674909734995</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.928176690730496</v>
+        <v>3.028084726749171</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.830279710810679</v>
+        <v>2.953976331838923</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.203779651148061</v>
+        <v>3.352469198925888</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.231102602961897</v>
+        <v>3.40310136252856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 552.3</t>
+          <t>X &lt; 552.4</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1656</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3912444223181026</v>
+        <v>-0.3965852548386763</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7992022242279049</v>
+        <v>0.7980154377832491</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5523005386779047</v>
+        <v>-0.5527950310559078</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2982987971152937</v>
+        <v>0.3468447168810656</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7164457736102818</v>
+        <v>0.7404031825598949</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.175213675213683</v>
+        <v>1.223225354204004</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.432782712586359</v>
+        <v>1.482030274980076</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.854892343503195</v>
+        <v>1.928149453282892</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.850384175192666</v>
+        <v>1.949731500487239</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.947615384082233</v>
+        <v>2.047523420100909</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.861220589577648</v>
+        <v>1.984917210605893</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.226093890853605</v>
+        <v>2.374783438631432</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.331056594220236</v>
+        <v>2.503055353786898</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 599.9</t>
+          <t>X &lt; 600</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6508063603070866</v>
+        <v>-0.6582599730351362</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3859355261451114</v>
+        <v>0.3796455628916391</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6363315802299994</v>
+        <v>-0.6408730522036947</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9054218958544169</v>
+        <v>-0.9098494098494214</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5309903993209062</v>
+        <v>-0.487417639120423</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2797892207306063</v>
+        <v>0.2981883925190232</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4232591238717447</v>
+        <v>0.4654525312137849</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.697776332908731</v>
+        <v>0.7403605115711827</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.036109635598734</v>
+        <v>1.102248301294786</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9848217576944336</v>
+        <v>1.076140518200603</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.8371656650360606</v>
+        <v>0.9859601846246235</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7574536861877377</v>
+        <v>0.930166808029405</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8507084232907545</v>
+        <v>1.04782939428609</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.019399007915467</v>
+        <v>1.239894199321398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 647.5</t>
+          <t>X &lt; 647.6</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1849</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8552307003166533</v>
+        <v>-0.860571532837227</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.09935271685611724</v>
+        <v>0.09816593041146149</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6740016857464113</v>
+        <v>-0.6741550757507326</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8141929834776818</v>
+        <v>-0.8146874758556848</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.541233212614479</v>
+        <v>-0.4926872928487072</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2428904113959547</v>
+        <v>0.2668478203455678</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4285964934494189</v>
+        <v>0.4766081724397395</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6646105970937199</v>
+        <v>0.7138581594874367</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.090378034946276</v>
+        <v>1.163635144725973</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8353754095196138</v>
+        <v>0.9347227348141871</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6847575395233463</v>
+        <v>0.7846655755420215</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5028025388229693</v>
+        <v>0.626499159851214</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.515317991620968</v>
+        <v>0.6640075393987956</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7951369301114255</v>
+        <v>0.9671356896780878</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 695.1</t>
+          <t>X &lt; 695.2</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1961</v>
+        <v>1972</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.086331276054352</v>
+        <v>-1.074343562922252</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4174949264364969</v>
+        <v>-0.413853426171876</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9371777679881106</v>
+        <v>-0.9318075337584446</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.033462164866329</v>
+        <v>-1.027173129594928</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.935547054916384</v>
+        <v>-0.9847059809317358</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4076197541472482</v>
+        <v>-0.4321923378617072</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4139815645648</v>
+        <v>-0.4654904613765041</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.04003938339834434</v>
+        <v>-0.09503971715564319</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3339272411103522</v>
+        <v>0.2498819861060184</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3265246037061473</v>
+        <v>0.2131925499894791</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2523666065701065</v>
+        <v>0.1387605019819063</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.06082387844094228</v>
+        <v>-0.07850143468139237</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1280794424203364</v>
+        <v>-0.03978791228712453</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2807803130169688</v>
+        <v>0.08575909995303022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 742.7</t>
+          <t>X &lt; 742.8</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.251815909624099</v>
+        <v>-1.240121232224709</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.159273362954849</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.812950176597418</v>
+        <v>-1.803411079148503</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.89452715264364</v>
+        <v>-1.884227171791942</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.839513948177938</v>
+        <v>-1.877494731365282</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.46960180291741</v>
+        <v>-1.48544051982276</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.766200278786087</v>
+        <v>-1.804073889256031</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.401714807786909</v>
+        <v>-1.442709769658613</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.199883661944483</v>
+        <v>-1.265490978625792</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.311905762459595</v>
+        <v>-1.402559249115136</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.395586332557464</v>
+        <v>-1.486398024973667</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.857943275891394</v>
+        <v>-1.969754389764134</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.824279282046383</v>
+        <v>-1.960873945543071</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.667608123531885</v>
+        <v>-1.827995125075255</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2246</v>
+        <v>2257</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.154616056554104</v>
+        <v>-1.144473058367154</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.124874488522892</v>
+        <v>-1.11841010880881</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.49617789470679</v>
+        <v>-1.48879056678787</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.519768932140742</v>
+        <v>-1.511973029176389</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.413784924512441</v>
+        <v>-1.448333745667597</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.048318102954838</v>
+        <v>-1.063672704441416</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.419957336706013</v>
+        <v>-1.454050554367036</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.019680369075893</v>
+        <v>-1.056789981999991</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7456426844071018</v>
+        <v>-0.8046187779860858</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9046882885754499</v>
+        <v>-0.9852220385179891</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9514723478780809</v>
+        <v>-1.032293603540666</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.337328415872172</v>
+        <v>-1.436662172345393</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.421523221818354</v>
+        <v>-1.541886437236649</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.438339132374757</v>
+        <v>-1.578636815930921</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2387</v>
+        <v>2398</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.421437659033074</v>
+        <v>-1.410982832767523</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.445165900171752</v>
+        <v>-1.437687250291795</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.026489855309016</v>
+        <v>-2.017122373658502</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.333285828260898</v>
+        <v>-2.322259136212622</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.474236749246195</v>
+        <v>-2.49907168234904</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.029714201377864</v>
+        <v>-2.038278133473696</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.3848640553446</v>
+        <v>-2.409730343969088</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.077884470885557</v>
+        <v>-2.105087009417105</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.824037422383086</v>
+        <v>-1.870318042058067</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.066099134804368</v>
+        <v>-2.130754970127029</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.122685588165254</v>
+        <v>-2.187527595277146</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.69352206142139</v>
+        <v>-2.773536895674297</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.839997435342589</v>
+        <v>-2.938043161824062</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.926867264685384</v>
+        <v>-3.041974119244159</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2531</v>
+        <v>2542</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.522066589850688</v>
+        <v>-1.51206877204941</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.909640464140843</v>
+        <v>-1.900649912392097</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.283883736520025</v>
+        <v>-2.273944250492278</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.723433095185953</v>
+        <v>-2.711374832064493</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.044544217073152</v>
+        <v>-3.062777729180631</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.766134191494466</v>
+        <v>-2.769684910648401</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.145631221486909</v>
+        <v>-3.163097405692369</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.198219517214518</v>
+        <v>-3.216264873625626</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3.080987508368978</v>
+        <v>-3.115081287059539</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.20028329186276</v>
+        <v>-3.250762976024184</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.265734268373834</v>
+        <v>-3.316313980124981</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.684179167446068</v>
+        <v>-3.748379662969889</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.04408263225924</v>
+        <v>-4.122948328595442</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.192662811716197</v>
+        <v>-4.286028140133588</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2675</v>
+        <v>2686</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.239890039985454</v>
+        <v>-1.231860620737301</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.617223076333573</v>
+        <v>-1.609967931540247</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.880767774920599</v>
+        <v>-1.873011325498808</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.326853206478084</v>
+        <v>-2.317083509961847</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.771241941705561</v>
+        <v>-2.787022795868431</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.603527361948913</v>
+        <v>-2.606271661161522</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.85527946747672</v>
+        <v>-2.870430411056077</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.818123197134405</v>
+        <v>-2.834122074798472</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.896892211980251</v>
+        <v>-2.925993987817066</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.018063926251202</v>
+        <v>-3.061268266048337</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.202958445259014</v>
+        <v>-3.245736111035967</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.484956091724335</v>
+        <v>-3.539905943293341</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.773288704844063</v>
+        <v>-3.841067976933573</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-4.051150277421826</v>
+        <v>-4.130868624903819</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2816</v>
+        <v>2827</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.24991061767571</v>
+        <v>-1.242506191084168</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.581493919920668</v>
+        <v>-1.574796483131955</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.851571067603309</v>
+        <v>-1.844320767279321</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.375048930936131</v>
+        <v>-2.365602497608144</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.576353847064091</v>
+        <v>-2.589692421225955</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.295864171511589</v>
+        <v>-2.298474204143581</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.574587389539104</v>
+        <v>-2.587685292566242</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.491653309421537</v>
+        <v>-2.505672455605442</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.569417568183987</v>
+        <v>-2.594695056665515</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.762371503705474</v>
+        <v>-2.799469461259605</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.019113147123377</v>
+        <v>-3.055496330330115</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.143270895458159</v>
+        <v>-3.190645414585582</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.367082630576839</v>
+        <v>-3.425649089093383</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.584072962213661</v>
+        <v>-3.653054039930339</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2960</v>
+        <v>2971</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.041602475716559</v>
+        <v>-1.035580993787789</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.366664707716623</v>
+        <v>-1.361140066596647</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.474419789066786</v>
+        <v>-1.468918246446073</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.730385738502235</v>
+        <v>-1.723798341879522</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.149905920555064</v>
+        <v>-2.161828239705521</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.801067931352151</v>
+        <v>-1.804220779376557</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.93539187472453</v>
+        <v>-1.947895879448261</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.946375932411215</v>
+        <v>-1.95934961171973</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.921960798222734</v>
+        <v>-1.944863636946181</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.180351806344241</v>
+        <v>-2.212997359172562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.333119150214351</v>
+        <v>-2.365440463346303</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.449337950643582</v>
+        <v>-2.490994009700529</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.6149189866995</v>
+        <v>-2.666227348034447</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.810117188257891</v>
+        <v>-2.870283865754011</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3101</v>
+        <v>3112</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.059684287164096</v>
+        <v>-1.054111824886981</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.634665567221688</v>
+        <v>-1.628500177648476</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.819778392671978</v>
+        <v>-1.813315723205449</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.961919981608318</v>
+        <v>-1.954836643177451</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.386899332651545</v>
+        <v>-2.395254542151172</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.233459674651975</v>
+        <v>-2.233862889532261</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.17262173783913</v>
+        <v>-2.181553366834109</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.300936067976153</v>
+        <v>-2.309845168525449</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.119533032347192</v>
+        <v>-2.137388759323983</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.501467676659189</v>
+        <v>-2.527006916782518</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.688914074556152</v>
+        <v>-2.713993627688737</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.766177549359114</v>
+        <v>-2.799227325989008</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.007906613729688</v>
+        <v>-3.048767635173135</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.184092017650322</v>
+        <v>-3.232417740856867</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3245</v>
+        <v>3256</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6631503662154046</v>
+        <v>-0.6593929506135012</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.098549774810948</v>
+        <v>-1.094512900250912</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.139207660687369</v>
+        <v>-1.135328092113276</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.330534693489895</v>
+        <v>-1.325911993701347</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.545214500528033</v>
+        <v>-1.553895826578703</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.446626292160289</v>
+        <v>-1.448606479275853</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.299740422153384</v>
+        <v>-1.30910167361931</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.412031294846507</v>
+        <v>-1.421370620117031</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.118017355493457</v>
+        <v>-1.135228011618516</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.42804932273981</v>
+        <v>-1.451694064848709</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.554353869386276</v>
+        <v>-1.577740249588231</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.626316773041736</v>
+        <v>-1.656287049142684</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.906417025592049</v>
+        <v>-1.942617655110908</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.156877276543405</v>
+        <v>-2.198929239502036</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3389</v>
+        <v>3400</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.7411025620313154</v>
+        <v>-0.7374777785933944</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.9606701918134135</v>
+        <v>-0.9572982887063759</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.928049978941452</v>
+        <v>-0.9250216213126876</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.017430947877536</v>
+        <v>-1.014034352744034</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.334019730691629</v>
+        <v>-1.340965186713142</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.197505012747101</v>
+        <v>-1.199193333735948</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.354830195665954</v>
+        <v>-1.361588661838567</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.33490990158765</v>
+        <v>-1.342021341803033</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.232717505078696</v>
+        <v>-1.245731667830562</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.595168689400687</v>
+        <v>-1.613070431879919</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.724850662768553</v>
+        <v>-1.742468644303763</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.792348035526878</v>
+        <v>-1.815277048525566</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.019449266771112</v>
+        <v>-2.047455970919884</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.338230799065514</v>
+        <v>-2.370630352379621</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3530</v>
+        <v>3541</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4584825362557652</v>
+        <v>-0.4560881895465201</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7041856922034953</v>
+        <v>-0.7017887693166927</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5473084137471744</v>
+        <v>-0.5455854569161005</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5995862178722078</v>
+        <v>-0.5976384921752498</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9248898816921454</v>
+        <v>-0.9308990403483008</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.7818487949524382</v>
+        <v>-0.7838065356297506</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9078891753966332</v>
+        <v>-0.9138567060435889</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.9355419863010042</v>
+        <v>-0.9416515735984987</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9246107620868642</v>
+        <v>-0.9351502843271575</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.193237618890485</v>
+        <v>-1.207723035056461</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.212581571878893</v>
+        <v>-1.227113715808187</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.162616680160454</v>
+        <v>-1.18166560016202</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.39724843118843</v>
+        <v>-1.420153508479423</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.63744664235788</v>
+        <v>-1.663884169015006</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3674</v>
+        <v>3685</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07732320283562899</v>
+        <v>-0.07636385301029947</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.2396875820897719</v>
+        <v>-0.2388123073920312</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1042412152731629</v>
+        <v>-0.1039100152406647</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.09503458854675984</v>
+        <v>0.0948192538179029</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2112561367038879</v>
+        <v>-0.2172636819063669</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.01949205962896627</v>
+        <v>0.01615793989554959</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1318803327945375</v>
+        <v>-0.1380545511665332</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1221689782348889</v>
+        <v>-0.1285429040675297</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08665013614037065</v>
+        <v>-0.09641753151738897</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3234303585410103</v>
+        <v>-0.3360659414441898</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2410124486789371</v>
+        <v>-0.2539740596480158</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.245800799981474</v>
+        <v>-0.2620099089642309</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4058197441656191</v>
+        <v>-0.4249798647412888</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6547044265577</v>
+        <v>-0.6763211497297661</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3815</v>
+        <v>3826</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2120524141121649</v>
+        <v>0.211951212362294</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.0756532984033953</v>
+        <v>0.07554902638238303</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4268745313749491</v>
+        <v>0.4256653090961962</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5714562103985372</v>
+        <v>0.5698644421272121</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3090369775369339</v>
+        <v>0.3035428128569819</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.463906161473723</v>
+        <v>0.4603006673073509</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4982595044706883</v>
+        <v>0.4922701734762498</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.490541955620337</v>
+        <v>0.4844558193408162</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.6797273082197961</v>
+        <v>0.6708151212320104</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.5514346057249782</v>
+        <v>0.5404089641922809</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6758617026899927</v>
+        <v>0.6644224225018576</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.7251575408470146</v>
+        <v>0.711311589174187</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.6081921499001837</v>
+        <v>0.5923016066443765</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4557518918313761</v>
+        <v>0.4380778669248215</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3959</v>
+        <v>3970</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2142622402619878</v>
+        <v>0.2139655037597592</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.07561381697094305</v>
+        <v>0.07547050733536054</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2990206981959034</v>
+        <v>0.2982029433907627</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.4430492920756635</v>
+        <v>0.4418521177315071</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3721991789136325</v>
+        <v>0.3684861119831311</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.381009340914936</v>
+        <v>0.3786308259026328</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.4362330646616641</v>
+        <v>0.4323705720568967</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4622586219624907</v>
+        <v>0.4582547717189698</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.6675760621887648</v>
+        <v>0.6616742003433203</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6392262542792935</v>
+        <v>0.6319570292259726</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6759939173463039</v>
+        <v>0.6685900157568483</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6995013145690194</v>
+        <v>0.6907128525633652</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6725146198830316</v>
+        <v>0.6624140504219866</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5085870299790471</v>
+        <v>0.4976464293658296</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0333806831382617</v>
+        <v>-0.03318127607688837</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04923802228303487</v>
+        <v>-0.04908196323690817</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1294480507210807</v>
+        <v>0.1291052687950369</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1998818496600876</v>
+        <v>0.199357750390547</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1623372466532231</v>
+        <v>0.1609001749727952</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.08307970026795175</v>
+        <v>0.08236239988777783</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1336243138348721</v>
+        <v>0.1322743964792394</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1189497916484612</v>
+        <v>0.1176132578339022</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1934319661046828</v>
+        <v>0.1913992152632105</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1379015926674327</v>
+        <v>0.1354772947435094</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1909983708086997</v>
+        <v>0.1884197035398358</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1659175249641223</v>
+        <v>0.1629130678026911</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1258390732074872</v>
+        <v>0.1224238658605898</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1211830665645977</v>
+        <v>0.1172968526071259</v>
       </c>
     </row>
   </sheetData>
